--- a/tests/comethyl_output/09a_me_trait_analysis/cov3_75pct/covMin4_methSD0p08/v2_exclude_protected_pcs/ME_Trait_Correlations_Bicor.xlsx
+++ b/tests/comethyl_output/09a_me_trait_analysis/cov3_75pct/covMin4_methSD0p08/v2_exclude_protected_pcs/ME_Trait_Correlations_Bicor.xlsx
@@ -600,19 +600,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
-        <v>0.280848625704894</v>
+        <v>0.278024902922421</v>
       </c>
       <c r="E2" t="n">
-        <v>1.97856336222604</v>
+        <v>1.93662811040973</v>
       </c>
       <c r="F2" t="n">
-        <v>2.00614431459071</v>
+        <v>1.96305219259921</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0506149858240233</v>
+        <v>0.0557031847811978</v>
       </c>
     </row>
     <row r="3">
@@ -623,19 +623,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.515073899744472</v>
+        <v>-0.496089317063126</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.79051502076809</v>
+        <v>-2.60943788855276</v>
       </c>
       <c r="F3" t="n">
-        <v>2.94388252860142</v>
+        <v>2.74011158734887</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00708808310766655</v>
+        <v>0.0116644409538978</v>
       </c>
     </row>
     <row r="4">
@@ -646,19 +646,19 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.281430554616998</v>
+        <v>0.279590185938174</v>
       </c>
       <c r="E4" t="n">
-        <v>1.41695633029461</v>
+        <v>1.37754242249671</v>
       </c>
       <c r="F4" t="n">
-        <v>1.43679549167328</v>
+        <v>1.39656315617596</v>
       </c>
       <c r="G4" t="n">
-        <v>0.163685434947895</v>
+        <v>0.175877457954007</v>
       </c>
     </row>
     <row r="5">
@@ -669,19 +669,19 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.281430554616999</v>
+        <v>-0.279590185938174</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.41695633029461</v>
+        <v>-1.37754242249671</v>
       </c>
       <c r="F5" t="n">
-        <v>1.43679549167328</v>
+        <v>1.39656315617596</v>
       </c>
       <c r="G5" t="n">
-        <v>0.163685434947895</v>
+        <v>0.175877457954006</v>
       </c>
     </row>
     <row r="6">
@@ -692,19 +692,19 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.281430554616998</v>
+        <v>0.279590185938174</v>
       </c>
       <c r="E6" t="n">
-        <v>1.41695633029461</v>
+        <v>1.37754242249671</v>
       </c>
       <c r="F6" t="n">
-        <v>1.43679549167328</v>
+        <v>1.39656315617596</v>
       </c>
       <c r="G6" t="n">
-        <v>0.163685434947895</v>
+        <v>0.175877457954007</v>
       </c>
     </row>
     <row r="7">
@@ -715,19 +715,19 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0141491353719596</v>
+        <v>0.03817481933966</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0970080589575987</v>
+        <v>0.259040105248475</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0970112962258202</v>
+        <v>0.259103088288272</v>
       </c>
       <c r="G7" t="n">
-        <v>0.923129933811737</v>
+        <v>0.796711715534931</v>
       </c>
     </row>
     <row r="8">
@@ -738,19 +738,19 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0436070465697948</v>
+        <v>0.066906816525862</v>
       </c>
       <c r="E8" t="n">
-        <v>0.299144560897324</v>
+        <v>0.454463057195136</v>
       </c>
       <c r="F8" t="n">
-        <v>0.299239497911471</v>
+        <v>0.454803217922867</v>
       </c>
       <c r="G8" t="n">
-        <v>0.766076585377133</v>
+        <v>0.651390000347563</v>
       </c>
     </row>
     <row r="9">
@@ -761,19 +761,19 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0164531330614687</v>
+        <v>0.0404905055960966</v>
       </c>
       <c r="E9" t="n">
-        <v>0.112807177276522</v>
+        <v>0.274770196017905</v>
       </c>
       <c r="F9" t="n">
-        <v>0.112812267853015</v>
+        <v>0.274845364439061</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910659866439844</v>
+        <v>0.784665744740567</v>
       </c>
     </row>
     <row r="10">
@@ -784,19 +784,19 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0518977267539162</v>
+        <v>-0.0334123411605208</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.356112834146476</v>
+        <v>-0.226697909068946</v>
       </c>
       <c r="F10" t="n">
-        <v>0.356273000895206</v>
+        <v>0.226740123187097</v>
       </c>
       <c r="G10" t="n">
-        <v>0.723230507025956</v>
+        <v>0.821630445250693</v>
       </c>
     </row>
     <row r="11">
@@ -807,19 +807,19 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0495132635405711</v>
+        <v>-0.0310373325995145</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.339723632691923</v>
+        <v>-0.210573064999483</v>
       </c>
       <c r="F11" t="n">
-        <v>0.339862686053368</v>
+        <v>0.210606896425593</v>
       </c>
       <c r="G11" t="n">
-        <v>0.735474129314958</v>
+        <v>0.834124196013807</v>
       </c>
     </row>
     <row r="12">
@@ -830,19 +830,19 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>0.120266511331719</v>
+        <v>0.138881191026912</v>
       </c>
       <c r="E12" t="n">
-        <v>0.828515746750994</v>
+        <v>0.948065160610158</v>
       </c>
       <c r="F12" t="n">
-        <v>0.830533975240058</v>
+        <v>0.951155667885428</v>
       </c>
       <c r="G12" t="n">
-        <v>0.410436114812576</v>
+        <v>0.34649646070502</v>
       </c>
     </row>
     <row r="13">
@@ -853,19 +853,19 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0167642209912229</v>
+        <v>-0.0424478325157808</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.113711131895888</v>
+        <v>-0.284919923970896</v>
       </c>
       <c r="F13" t="n">
-        <v>0.113716459181356</v>
+        <v>0.28500559694986</v>
       </c>
       <c r="G13" t="n">
-        <v>0.909957437535727</v>
+        <v>0.776947479121615</v>
       </c>
     </row>
     <row r="14">
@@ -876,19 +876,19 @@
         <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.108492954939881</v>
+        <v>-0.129659288639217</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.746729326751221</v>
+        <v>-0.884370369621222</v>
       </c>
       <c r="F14" t="n">
-        <v>0.748206726884673</v>
+        <v>0.8868785725068</v>
       </c>
       <c r="G14" t="n">
-        <v>0.458063253077948</v>
+        <v>0.379757748538786</v>
       </c>
     </row>
     <row r="15">
@@ -899,19 +899,19 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.071600301557033</v>
+        <v>-0.0878953068732491</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.491708353111426</v>
+        <v>-0.597677294512618</v>
       </c>
       <c r="F15" t="n">
-        <v>0.492130035394048</v>
+        <v>0.598451149911768</v>
       </c>
       <c r="G15" t="n">
-        <v>0.624918356508431</v>
+        <v>0.552474516872556</v>
       </c>
     </row>
     <row r="16">
@@ -922,19 +922,19 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.296045814906635</v>
+        <v>-0.302641652371087</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.09220850383557</v>
+        <v>-2.11896983394365</v>
       </c>
       <c r="F16" t="n">
-        <v>2.12483631594728</v>
+        <v>2.15361036607498</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03888772500955</v>
+        <v>0.0365458322840949</v>
       </c>
     </row>
     <row r="17">
@@ -945,19 +945,19 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.140698879767121</v>
+        <v>-0.152414029316352</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.950139935985616</v>
+        <v>-1.01893977860386</v>
       </c>
       <c r="F17" t="n">
-        <v>0.953319990554412</v>
+        <v>1.0229517146158</v>
       </c>
       <c r="G17" t="n">
-        <v>0.345520965121465</v>
+        <v>0.311922201605004</v>
       </c>
     </row>
     <row r="18">
@@ -968,19 +968,19 @@
         <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.128018252731913</v>
+        <v>-0.14107337653219</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.772347365307352</v>
+        <v>-0.84020508005753</v>
       </c>
       <c r="F18" t="n">
-        <v>0.774482100762252</v>
+        <v>0.843032397591358</v>
       </c>
       <c r="G18" t="n">
-        <v>0.443702865802179</v>
+        <v>0.404934940009205</v>
       </c>
     </row>
     <row r="19">
@@ -991,19 +991,19 @@
         <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.138999568422402</v>
+        <v>-0.145195869438734</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.884838742603721</v>
+        <v>-0.913201719345709</v>
       </c>
       <c r="F19" t="n">
-        <v>0.887728132641782</v>
+        <v>0.91645970087951</v>
       </c>
       <c r="G19" t="n">
-        <v>0.379994005112684</v>
+        <v>0.365058375893893</v>
       </c>
     </row>
     <row r="20">
@@ -1014,19 +1014,19 @@
         <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.220005828552102</v>
+        <v>-0.229694491276016</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.28484171506317</v>
+        <v>-1.32295106806757</v>
       </c>
       <c r="F20" t="n">
-        <v>1.29558086497527</v>
+        <v>1.33504361264436</v>
       </c>
       <c r="G20" t="n">
-        <v>0.204109582895267</v>
+        <v>0.191282702123905</v>
       </c>
     </row>
     <row r="21">
@@ -1037,19 +1037,19 @@
         <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.135201701091266</v>
+        <v>-0.141626430706634</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.860358748624991</v>
+        <v>-0.89044247147171</v>
       </c>
       <c r="F21" t="n">
-        <v>0.863014756310521</v>
+        <v>0.893462723615733</v>
       </c>
       <c r="G21" t="n">
-        <v>0.393274511339787</v>
+        <v>0.377089906846795</v>
       </c>
     </row>
     <row r="22">
@@ -1063,16 +1063,16 @@
         <v>29</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.25342683834346</v>
+        <v>-0.250915805767467</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.34617482461758</v>
+        <v>-1.33224105356877</v>
       </c>
       <c r="F22" t="n">
-        <v>1.36128420696642</v>
+        <v>1.34688508814163</v>
       </c>
       <c r="G22" t="n">
-        <v>0.18467733065806</v>
+        <v>0.189214437781617</v>
       </c>
     </row>
     <row r="23">
@@ -1083,19 +1083,19 @@
         <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.155276409136386</v>
+        <v>-0.153229143840271</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.964994157279725</v>
+        <v>-0.939455651234339</v>
       </c>
       <c r="F23" t="n">
-        <v>0.968940286675115</v>
+        <v>0.943194981556206</v>
       </c>
       <c r="G23" t="n">
-        <v>0.338702018527726</v>
+        <v>0.35169954388831</v>
       </c>
     </row>
     <row r="24">
@@ -1106,19 +1106,19 @@
         <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.333960216342577</v>
+        <v>-0.325930711359295</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.11241568639184</v>
+        <v>-2.0296110232128</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1551329725877</v>
+        <v>2.06853964857648</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0377278688166482</v>
+        <v>0.0458296420509902</v>
       </c>
     </row>
     <row r="25">
@@ -1129,19 +1129,19 @@
         <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0824916195277424</v>
+        <v>-0.094780176964065</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.554630960970694</v>
+        <v>-0.630593379978538</v>
       </c>
       <c r="F25" t="n">
-        <v>0.55526307728979</v>
+        <v>0.63154363579896</v>
       </c>
       <c r="G25" t="n">
-        <v>0.581464695910409</v>
+        <v>0.530952697418384</v>
       </c>
     </row>
     <row r="26">
@@ -1152,19 +1152,19 @@
         <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0922959783757364</v>
+        <v>0.0947917042926321</v>
       </c>
       <c r="E26" t="n">
-        <v>0.585397058239411</v>
+        <v>0.593756678720145</v>
       </c>
       <c r="F26" t="n">
-        <v>0.586233289500179</v>
+        <v>0.594651643526586</v>
       </c>
       <c r="G26" t="n">
-        <v>0.561012537922668</v>
+        <v>0.55551082940541</v>
       </c>
     </row>
     <row r="27">
@@ -1175,19 +1175,19 @@
         <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.116170006286139</v>
+        <v>-0.122838078747971</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.690387985613233</v>
+        <v>-0.719898510032146</v>
       </c>
       <c r="F27" t="n">
-        <v>0.69195602183282</v>
+        <v>0.721728777848264</v>
       </c>
       <c r="G27" t="n">
-        <v>0.49353011891644</v>
+        <v>0.475395750560665</v>
       </c>
     </row>
     <row r="28">
@@ -1198,19 +1198,19 @@
         <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0521789425152378</v>
+        <v>-0.0478149278003866</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.308975400602124</v>
+        <v>-0.279019311231754</v>
       </c>
       <c r="F28" t="n">
-        <v>0.309115879679421</v>
+        <v>0.27912580454542</v>
       </c>
       <c r="G28" t="n">
-        <v>0.759066087665746</v>
+        <v>0.781839164851595</v>
       </c>
     </row>
     <row r="29">
@@ -1221,19 +1221,19 @@
         <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0453763652683189</v>
+        <v>-0.0452743317970442</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.283570042198723</v>
+        <v>-0.279280649230964</v>
       </c>
       <c r="F29" t="n">
-        <v>0.283667498507544</v>
+        <v>0.279376199576093</v>
       </c>
       <c r="G29" t="n">
-        <v>0.778165716042483</v>
+        <v>0.781471139951486</v>
       </c>
     </row>
     <row r="30">
@@ -1244,19 +1244,19 @@
         <v>36</v>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0561330030491808</v>
+        <v>-0.0480502614451557</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.346391192514612</v>
+        <v>-0.292503582107261</v>
       </c>
       <c r="F30" t="n">
-        <v>0.346573512484671</v>
+        <v>0.292616325423547</v>
       </c>
       <c r="G30" t="n">
-        <v>0.730823602033016</v>
+        <v>0.771450170693037</v>
       </c>
     </row>
     <row r="31">
@@ -1267,19 +1267,19 @@
         <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.185643192927906</v>
+        <v>-0.182090717545861</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.06247624055566</v>
+        <v>-1.02527183565953</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0687340515914</v>
+        <v>1.0310760098169</v>
       </c>
       <c r="G31" t="n">
-        <v>0.293185588102708</v>
+        <v>0.310482869517928</v>
       </c>
     </row>
     <row r="32">
@@ -1290,19 +1290,19 @@
         <v>38</v>
       </c>
       <c r="C32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.112325184988605</v>
+        <v>-0.108876087647941</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.617837584648073</v>
+        <v>-0.588649023018093</v>
       </c>
       <c r="F32" t="n">
-        <v>0.619148657314762</v>
+        <v>0.58982197299205</v>
       </c>
       <c r="G32" t="n">
-        <v>0.540492153055004</v>
+        <v>0.559877945379259</v>
       </c>
     </row>
     <row r="33">
@@ -1313,19 +1313,19 @@
         <v>39</v>
       </c>
       <c r="C33" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.164921473924175</v>
+        <v>-0.162533782934319</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0394274455404</v>
+        <v>-1.01089076364934</v>
       </c>
       <c r="F33" t="n">
-        <v>1.04423327351817</v>
+        <v>1.01542769047195</v>
       </c>
       <c r="G33" t="n">
-        <v>0.302807096141776</v>
+        <v>0.316323979866866</v>
       </c>
     </row>
     <row r="34">
@@ -1336,19 +1336,19 @@
         <v>40</v>
       </c>
       <c r="C34" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.211434848347591</v>
+        <v>-0.198451240235238</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.34063161477449</v>
+        <v>-1.23978559801906</v>
       </c>
       <c r="F34" t="n">
-        <v>1.35095241017416</v>
+        <v>1.24816056713797</v>
       </c>
       <c r="G34" t="n">
-        <v>0.184496834392418</v>
+        <v>0.219608447997965</v>
       </c>
     </row>
     <row r="35">
@@ -1362,16 +1362,16 @@
         <v>28</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.193996454483131</v>
+        <v>-0.191041929242005</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.00188896447857</v>
+        <v>-0.986243906710772</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0083480715232</v>
+        <v>0.992404758009787</v>
       </c>
       <c r="G35" t="n">
-        <v>0.322580045537724</v>
+        <v>0.33014680606043</v>
       </c>
     </row>
     <row r="36">
@@ -1385,16 +1385,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.170279469509708</v>
+        <v>-0.168581343280858</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.876799168045893</v>
+        <v>-0.867884475810679</v>
       </c>
       <c r="F36" t="n">
-        <v>0.881126476313983</v>
+        <v>0.872081004712802</v>
       </c>
       <c r="G36" t="n">
-        <v>0.386322376107702</v>
+        <v>0.391146587057453</v>
       </c>
     </row>
     <row r="37">
@@ -1405,19 +1405,19 @@
         <v>43</v>
       </c>
       <c r="C37" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0671136675601881</v>
+        <v>-0.0616533361073618</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.41433927620284</v>
+        <v>-0.375498859774886</v>
       </c>
       <c r="F37" t="n">
-        <v>0.414651331504038</v>
+        <v>0.375737396714627</v>
       </c>
       <c r="G37" t="n">
-        <v>0.68072878613956</v>
+        <v>0.709257829762439</v>
       </c>
     </row>
     <row r="38">
@@ -1428,19 +1428,19 @@
         <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.288865978543925</v>
+        <v>-0.277790597236312</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.80857900925786</v>
+        <v>-1.71171792364215</v>
       </c>
       <c r="F38" t="n">
-        <v>1.8353447308056</v>
+        <v>1.73503155882255</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0745028289514647</v>
+        <v>0.0912902511116592</v>
       </c>
     </row>
     <row r="39">
@@ -1451,19 +1451,19 @@
         <v>45</v>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.13701696847042</v>
+        <v>-0.127088822838096</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.72961457631344</v>
+        <v>-0.66396310473027</v>
       </c>
       <c r="F39" t="n">
-        <v>0.731928686615357</v>
+        <v>0.665771408428544</v>
       </c>
       <c r="G39" t="n">
-        <v>0.470294430144875</v>
+        <v>0.511205575857558</v>
       </c>
     </row>
     <row r="40">
@@ -1474,19 +1474,19 @@
         <v>46</v>
       </c>
       <c r="C40" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D40" t="n">
-        <v>0.059261140750922</v>
+        <v>0.0674868476531</v>
       </c>
       <c r="E40" t="n">
-        <v>0.340828693362427</v>
+        <v>0.382344426929152</v>
       </c>
       <c r="F40" t="n">
-        <v>0.341028688619692</v>
+        <v>0.382635607413485</v>
       </c>
       <c r="G40" t="n">
-        <v>0.735243807670072</v>
+        <v>0.704519786730054</v>
       </c>
     </row>
     <row r="41">
@@ -1497,19 +1497,19 @@
         <v>47</v>
       </c>
       <c r="C41" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.276737816561957</v>
+        <v>-0.273473764444949</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.53017232258814</v>
+        <v>-1.48487262302896</v>
       </c>
       <c r="F41" t="n">
-        <v>1.55084633782908</v>
+        <v>1.50443709241295</v>
       </c>
       <c r="G41" t="n">
-        <v>0.131784379185218</v>
+        <v>0.143666438987545</v>
       </c>
     </row>
     <row r="42">
@@ -1520,19 +1520,19 @@
         <v>48</v>
       </c>
       <c r="C42" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D42" t="n">
-        <v>0.245709085346024</v>
+        <v>0.245064363113495</v>
       </c>
       <c r="E42" t="n">
-        <v>1.35082031705145</v>
+        <v>1.32369586062151</v>
       </c>
       <c r="F42" t="n">
-        <v>1.36503082881164</v>
+        <v>1.3375447231075</v>
       </c>
       <c r="G42" t="n">
-        <v>0.182740669051505</v>
+        <v>0.191808870923904</v>
       </c>
     </row>
     <row r="43">
@@ -1546,16 +1546,16 @@
         <v>15</v>
       </c>
       <c r="D43" t="n">
-        <v>0.104501979121294</v>
+        <v>0.102636961037731</v>
       </c>
       <c r="E43" t="n">
-        <v>0.37816789093021</v>
+        <v>0.371370558034698</v>
       </c>
       <c r="F43" t="n">
-        <v>0.378861633314907</v>
+        <v>0.372027547151054</v>
       </c>
       <c r="G43" t="n">
-        <v>0.710906121992023</v>
+        <v>0.715866219967345</v>
       </c>
     </row>
     <row r="44">
@@ -1569,16 +1569,16 @@
         <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>0.061698814038347</v>
+        <v>0.0615786268951237</v>
       </c>
       <c r="E44" t="n">
-        <v>0.289761145854104</v>
+        <v>0.289195268225807</v>
       </c>
       <c r="F44" t="n">
-        <v>0.289945490017747</v>
+        <v>0.289378534337766</v>
       </c>
       <c r="G44" t="n">
-        <v>0.774573165679813</v>
+        <v>0.775001264693049</v>
       </c>
     </row>
     <row r="45">
@@ -1589,19 +1589,19 @@
         <v>51</v>
       </c>
       <c r="C45" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0967522761752838</v>
+        <v>-0.120578685411064</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.504317159991529</v>
+        <v>-0.617839067611066</v>
       </c>
       <c r="F45" t="n">
-        <v>0.505109297849908</v>
+        <v>0.619352002734033</v>
       </c>
       <c r="G45" t="n">
-        <v>0.617580418555407</v>
+        <v>0.541074256572828</v>
       </c>
     </row>
     <row r="46">
@@ -1612,19 +1612,19 @@
         <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.13040863707199</v>
+        <v>-0.129976404637733</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.753431183056509</v>
+        <v>-0.739440506598482</v>
       </c>
       <c r="F46" t="n">
-        <v>0.75559310050372</v>
+        <v>0.741548064466151</v>
       </c>
       <c r="G46" t="n">
-        <v>0.455252966854448</v>
+        <v>0.463769103398516</v>
       </c>
     </row>
     <row r="47">
@@ -1635,19 +1635,19 @@
         <v>53</v>
       </c>
       <c r="C47" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0423893485115812</v>
+        <v>-0.0530889209201961</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.220393584518831</v>
+        <v>-0.270956192670445</v>
       </c>
       <c r="F47" t="n">
-        <v>0.220459672258078</v>
+        <v>0.271083729014039</v>
       </c>
       <c r="G47" t="n">
-        <v>0.827171714566406</v>
+        <v>0.788467271380275</v>
       </c>
     </row>
     <row r="48">
@@ -1658,19 +1658,19 @@
         <v>54</v>
       </c>
       <c r="C48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0715737413582084</v>
+        <v>-0.0616392335766986</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.372545099010464</v>
+        <v>-0.314698614213289</v>
       </c>
       <c r="F48" t="n">
-        <v>0.372864350674566</v>
+        <v>0.314898435892898</v>
       </c>
       <c r="G48" t="n">
-        <v>0.71216062208005</v>
+        <v>0.755352118536561</v>
       </c>
     </row>
     <row r="49">
@@ -1684,16 +1684,16 @@
         <v>15</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0586765874054822</v>
+        <v>0.0598462749411201</v>
       </c>
       <c r="E49" t="n">
-        <v>0.21180474528128</v>
+        <v>0.216036977405526</v>
       </c>
       <c r="F49" t="n">
-        <v>0.211926584579565</v>
+        <v>0.216166268208687</v>
       </c>
       <c r="G49" t="n">
-        <v>0.835450808898746</v>
+        <v>0.83221312609991</v>
       </c>
     </row>
     <row r="50">
@@ -1707,16 +1707,16 @@
         <v>23</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.315446151411623</v>
+        <v>-0.316544948649872</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.49658640469177</v>
+        <v>-1.50218029477846</v>
       </c>
       <c r="F50" t="n">
-        <v>1.52333189398517</v>
+        <v>1.52922789158322</v>
       </c>
       <c r="G50" t="n">
-        <v>0.142593755534428</v>
+        <v>0.14113233145878</v>
       </c>
     </row>
     <row r="51">
@@ -1727,19 +1727,19 @@
         <v>57</v>
       </c>
       <c r="C51" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0134620877917932</v>
+        <v>0.0197602286584063</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0829908961546261</v>
+        <v>0.120212426416917</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0829934031899402</v>
+        <v>0.120220251763767</v>
       </c>
       <c r="G51" t="n">
-        <v>0.934292438608868</v>
+        <v>0.904959129115703</v>
       </c>
     </row>
     <row r="52">
@@ -1750,19 +1750,19 @@
         <v>58</v>
       </c>
       <c r="C52" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.120628301938816</v>
+        <v>-0.116519930307413</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.737343708293508</v>
+        <v>-0.702309566016684</v>
       </c>
       <c r="F52" t="n">
-        <v>0.739150782683883</v>
+        <v>0.703914397777439</v>
       </c>
       <c r="G52" t="n">
-        <v>0.464479099990665</v>
+        <v>0.486014565652706</v>
       </c>
     </row>
     <row r="53">
@@ -1773,19 +1773,19 @@
         <v>59</v>
       </c>
       <c r="C53" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D53" t="n">
-        <v>0.111364893630765</v>
+        <v>0.117442124827423</v>
       </c>
       <c r="E53" t="n">
-        <v>0.670972426801898</v>
+        <v>0.698018043373529</v>
       </c>
       <c r="F53" t="n">
-        <v>0.672371794427627</v>
+        <v>0.69963866986737</v>
       </c>
       <c r="G53" t="n">
-        <v>0.505639925976008</v>
+        <v>0.488777228358662</v>
       </c>
     </row>
     <row r="54">
@@ -1796,19 +1796,19 @@
         <v>60</v>
       </c>
       <c r="C54" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.0338643682463272</v>
+        <v>-0.0333594321359644</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.200420941733561</v>
+        <v>-0.194589448524745</v>
       </c>
       <c r="F54" t="n">
-        <v>0.200459280216343</v>
+        <v>0.194625568868726</v>
       </c>
       <c r="G54" t="n">
-        <v>0.842281699608109</v>
+        <v>0.846844387604366</v>
       </c>
     </row>
     <row r="55">
@@ -1819,19 +1819,19 @@
         <v>61</v>
       </c>
       <c r="C55" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.00811611608246402</v>
+        <v>-0.00406626827600317</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0556425103285053</v>
+        <v>-0.0275789252500304</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0556431212318</v>
+        <v>0.0275790012517277</v>
       </c>
       <c r="G55" t="n">
-        <v>0.955861982850575</v>
+        <v>0.978117232910363</v>
       </c>
     </row>
     <row r="56">
@@ -1842,19 +1842,19 @@
         <v>62</v>
       </c>
       <c r="C56" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D56" t="n">
-        <v>0.145246886330969</v>
+        <v>0.13514236802212</v>
       </c>
       <c r="E56" t="n">
-        <v>0.901739242141344</v>
+        <v>0.827098921989639</v>
       </c>
       <c r="F56" t="n">
-        <v>0.90495862559668</v>
+        <v>0.829649983112712</v>
       </c>
       <c r="G56" t="n">
-        <v>0.37118937303569</v>
+        <v>0.412057632608899</v>
       </c>
     </row>
     <row r="57">
@@ -1865,19 +1865,19 @@
         <v>63</v>
       </c>
       <c r="C57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00160775877403993</v>
+        <v>-0.00752097437408568</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00991089923961645</v>
+        <v>-0.0457491637283622</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0099109035093854</v>
+        <v>0.0457495950465118</v>
       </c>
       <c r="G57" t="n">
-        <v>0.99214422309447</v>
+        <v>0.963755869733466</v>
       </c>
     </row>
     <row r="58">
@@ -1891,16 +1891,16 @@
         <v>40</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.00941020119777761</v>
+        <v>-0.00857618478520926</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.0580100883756938</v>
+        <v>-0.0528684497822396</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0580109445804919</v>
+        <v>0.0528690979038143</v>
       </c>
       <c r="G58" t="n">
-        <v>0.954043896888734</v>
+        <v>0.9581131702421</v>
       </c>
     </row>
     <row r="59">
@@ -1914,16 +1914,16 @@
         <v>40</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.0970720375842447</v>
+        <v>-0.0958963008863763</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.600282472483251</v>
+        <v>-0.592966639327878</v>
       </c>
       <c r="F59" t="n">
-        <v>0.601231629474247</v>
+        <v>0.593881503996173</v>
       </c>
       <c r="G59" t="n">
-        <v>0.551255693729079</v>
+        <v>0.556110487918274</v>
       </c>
     </row>
     <row r="60">
@@ -1934,19 +1934,19 @@
         <v>66</v>
       </c>
       <c r="C60" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.0215137373305774</v>
+        <v>-0.0317179601898025</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.145935783541999</v>
+        <v>-0.212841939488704</v>
       </c>
       <c r="F60" t="n">
-        <v>0.145947044785626</v>
+        <v>0.2128776527671</v>
       </c>
       <c r="G60" t="n">
-        <v>0.884600890597005</v>
+        <v>0.832383838522261</v>
       </c>
     </row>
     <row r="61">
@@ -1957,19 +1957,19 @@
         <v>67</v>
       </c>
       <c r="C61" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D61" t="n">
-        <v>0.092008451136135</v>
+        <v>0.120717491182</v>
       </c>
       <c r="E61" t="n">
-        <v>0.632567219783829</v>
+        <v>0.822758116532558</v>
       </c>
       <c r="F61" t="n">
-        <v>0.63346517733957</v>
+        <v>0.824777538097876</v>
       </c>
       <c r="G61" t="n">
-        <v>0.529500608071554</v>
+        <v>0.413754501372073</v>
       </c>
     </row>
     <row r="62">
@@ -1980,19 +1980,19 @@
         <v>68</v>
       </c>
       <c r="C62" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.0454484601840523</v>
+        <v>-0.0370898893895566</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.311793740006581</v>
+        <v>-0.251671315955513</v>
       </c>
       <c r="F62" t="n">
-        <v>0.311901237411695</v>
+        <v>0.251729075262973</v>
       </c>
       <c r="G62" t="n">
-        <v>0.756495068506589</v>
+        <v>0.802371750267545</v>
       </c>
     </row>
     <row r="63">
@@ -2003,19 +2003,19 @@
         <v>69</v>
       </c>
       <c r="C63" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0787337622240973</v>
+        <v>0.0994090518127343</v>
       </c>
       <c r="E63" t="n">
-        <v>0.540890994843886</v>
+        <v>0.676459187935916</v>
       </c>
       <c r="F63" t="n">
-        <v>0.541452321042583</v>
+        <v>0.677581288363916</v>
       </c>
       <c r="G63" t="n">
-        <v>0.590753404647543</v>
+        <v>0.501431169411024</v>
       </c>
     </row>
     <row r="64">
@@ -2026,19 +2026,19 @@
         <v>70</v>
       </c>
       <c r="C64" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.0655289975111622</v>
+        <v>-0.0478660045757103</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.44988886063044</v>
+        <v>-0.324891315174862</v>
       </c>
       <c r="F64" t="n">
-        <v>0.45021182909831</v>
+        <v>0.325015581956912</v>
       </c>
       <c r="G64" t="n">
-        <v>0.654627574506796</v>
+        <v>0.746642902994758</v>
       </c>
     </row>
     <row r="65">
@@ -2049,19 +2049,19 @@
         <v>71</v>
       </c>
       <c r="C65" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0772927224485839</v>
+        <v>0.103920255614586</v>
       </c>
       <c r="E65" t="n">
-        <v>0.530951228038723</v>
+        <v>0.707375254608952</v>
       </c>
       <c r="F65" t="n">
-        <v>0.531482167525893</v>
+        <v>0.708658402497166</v>
       </c>
       <c r="G65" t="n">
-        <v>0.597587819448421</v>
+        <v>0.48211255381825</v>
       </c>
     </row>
     <row r="66">
@@ -2072,19 +2072,19 @@
         <v>72</v>
       </c>
       <c r="C66" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0287982466495702</v>
+        <v>0.0551574450184503</v>
       </c>
       <c r="E66" t="n">
-        <v>0.197485438331712</v>
+        <v>0.374476063366467</v>
       </c>
       <c r="F66" t="n">
-        <v>0.197512751629851</v>
+        <v>0.374666359210531</v>
       </c>
       <c r="G66" t="n">
-        <v>0.844278044122275</v>
+        <v>0.709630404771662</v>
       </c>
     </row>
     <row r="67">
@@ -2095,19 +2095,19 @@
         <v>73</v>
       </c>
       <c r="C67" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0580974925339155</v>
+        <v>0.0855748192912034</v>
       </c>
       <c r="E67" t="n">
-        <v>0.398745377384804</v>
+        <v>0.581819678288384</v>
       </c>
       <c r="F67" t="n">
-        <v>0.398970236933635</v>
+        <v>0.582533543030827</v>
       </c>
       <c r="G67" t="n">
-        <v>0.691722155469928</v>
+        <v>0.563052073818652</v>
       </c>
     </row>
     <row r="68">
@@ -2118,19 +2118,19 @@
         <v>8</v>
       </c>
       <c r="C68" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.291831197021003</v>
+        <v>-0.284759382666505</v>
       </c>
       <c r="E68" t="n">
-        <v>-2.06058194502606</v>
+        <v>-1.98623149884413</v>
       </c>
       <c r="F68" t="n">
-        <v>2.09174801685831</v>
+        <v>2.01474448152851</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0418903392530171</v>
+        <v>0.0497985408504496</v>
       </c>
     </row>
     <row r="69">
@@ -2141,19 +2141,19 @@
         <v>9</v>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D69" t="n">
-        <v>0.559293550374664</v>
+        <v>0.535795567871452</v>
       </c>
       <c r="E69" t="n">
-        <v>3.09519762401933</v>
+        <v>2.86905529947725</v>
       </c>
       <c r="F69" t="n">
-        <v>3.30526882642754</v>
+        <v>3.04327843444062</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00297341444136559</v>
+        <v>0.00577173078303921</v>
       </c>
     </row>
     <row r="70">
@@ -2164,19 +2164,19 @@
         <v>10</v>
       </c>
       <c r="C70" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.276015255471691</v>
+        <v>-0.270994201471318</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.3881922146396</v>
+        <v>-1.33293668318185</v>
       </c>
       <c r="F70" t="n">
-        <v>1.40684440056481</v>
+        <v>1.35016436149993</v>
       </c>
       <c r="G70" t="n">
-        <v>0.172291777823962</v>
+        <v>0.190101078944172</v>
       </c>
     </row>
     <row r="71">
@@ -2187,19 +2187,19 @@
         <v>11</v>
       </c>
       <c r="C71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D71" t="n">
-        <v>0.276015255471691</v>
+        <v>0.270994201471319</v>
       </c>
       <c r="E71" t="n">
-        <v>1.3881922146396</v>
+        <v>1.33293668318186</v>
       </c>
       <c r="F71" t="n">
-        <v>1.40684440056481</v>
+        <v>1.35016436149993</v>
       </c>
       <c r="G71" t="n">
-        <v>0.172291777823962</v>
+        <v>0.190101078944171</v>
       </c>
     </row>
     <row r="72">
@@ -2210,19 +2210,19 @@
         <v>12</v>
       </c>
       <c r="C72" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.276015255471691</v>
+        <v>-0.270994201471318</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3881922146396</v>
+        <v>-1.33293668318185</v>
       </c>
       <c r="F72" t="n">
-        <v>1.40684440056481</v>
+        <v>1.35016436149993</v>
       </c>
       <c r="G72" t="n">
-        <v>0.172291777823962</v>
+        <v>0.190101078944172</v>
       </c>
     </row>
     <row r="73">
@@ -2233,19 +2233,19 @@
         <v>13</v>
       </c>
       <c r="C73" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0055781212824211</v>
+        <v>-0.0477244251029261</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.0382420694742847</v>
+        <v>-0.323928877895041</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0382422677984914</v>
+        <v>0.324052043501815</v>
       </c>
       <c r="G73" t="n">
-        <v>0.969656498190253</v>
+        <v>0.74736751928195</v>
       </c>
     </row>
     <row r="74">
@@ -2256,19 +2256,19 @@
         <v>14</v>
       </c>
       <c r="C74" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0350458235137011</v>
+        <v>-0.0777038972284914</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.240360497815591</v>
+        <v>-0.52807801532459</v>
       </c>
       <c r="F74" t="n">
-        <v>0.240409743351525</v>
+        <v>0.528611739433793</v>
       </c>
       <c r="G74" t="n">
-        <v>0.811058187600871</v>
+        <v>0.599616200044715</v>
       </c>
     </row>
     <row r="75">
@@ -2279,19 +2279,19 @@
         <v>15</v>
       </c>
       <c r="C75" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.00786254120548682</v>
+        <v>-0.0501608248446627</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.0539039775778384</v>
+        <v>-0.340493030635922</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0539045329890895</v>
+        <v>0.340636074860299</v>
       </c>
       <c r="G75" t="n">
-        <v>0.957239704624591</v>
+        <v>0.734928415680886</v>
       </c>
     </row>
     <row r="76">
@@ -2302,19 +2302,19 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0798105004814074</v>
+        <v>0.0480422262676139</v>
       </c>
       <c r="E76" t="n">
-        <v>0.548319421928687</v>
+        <v>0.326089263641589</v>
       </c>
       <c r="F76" t="n">
-        <v>0.548904199470277</v>
+        <v>0.32621491020484</v>
       </c>
       <c r="G76" t="n">
-        <v>0.585669595939706</v>
+        <v>0.745741287311296</v>
       </c>
     </row>
     <row r="77">
@@ -2325,19 +2325,19 @@
         <v>17</v>
       </c>
       <c r="C77" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0776589914629774</v>
+        <v>0.0456946651099401</v>
       </c>
       <c r="E77" t="n">
-        <v>0.533477405321545</v>
+        <v>0.310132269872302</v>
       </c>
       <c r="F77" t="n">
-        <v>0.534015960827307</v>
+        <v>0.310240357801074</v>
       </c>
       <c r="G77" t="n">
-        <v>0.595847423050557</v>
+        <v>0.757779467760475</v>
       </c>
     </row>
     <row r="78">
@@ -2348,19 +2348,19 @@
         <v>18</v>
       </c>
       <c r="C78" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.144921431841053</v>
+        <v>-0.178917886573082</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.00057572025536</v>
+        <v>-1.22668316423415</v>
       </c>
       <c r="F78" t="n">
-        <v>1.00413173299377</v>
+        <v>1.23338198621143</v>
       </c>
       <c r="G78" t="n">
-        <v>0.320456994162317</v>
+        <v>0.223698748406871</v>
       </c>
     </row>
     <row r="79">
@@ -2371,19 +2371,19 @@
         <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.0201128804017401</v>
+        <v>0.0225935312741952</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.136430590443401</v>
+        <v>0.151587812413082</v>
       </c>
       <c r="F79" t="n">
-        <v>0.136439791442339</v>
+        <v>0.151600713912323</v>
       </c>
       <c r="G79" t="n">
-        <v>0.892069010412829</v>
+        <v>0.880179490090556</v>
       </c>
     </row>
     <row r="80">
@@ -2394,19 +2394,19 @@
         <v>20</v>
       </c>
       <c r="C80" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0847154054344444</v>
+        <v>0.117422870764922</v>
       </c>
       <c r="E80" t="n">
-        <v>0.582174932649047</v>
+        <v>0.80009153179267</v>
       </c>
       <c r="F80" t="n">
-        <v>0.582874884207689</v>
+        <v>0.801948532723728</v>
       </c>
       <c r="G80" t="n">
-        <v>0.562763847001641</v>
+        <v>0.426706319553373</v>
       </c>
     </row>
     <row r="81">
@@ -2417,19 +2417,19 @@
         <v>21</v>
       </c>
       <c r="C81" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0932916294979349</v>
+        <v>0.116752056057118</v>
       </c>
       <c r="E81" t="n">
-        <v>0.641440416468997</v>
+        <v>0.795478604091415</v>
       </c>
       <c r="F81" t="n">
-        <v>0.642376705524066</v>
+        <v>0.797303655635311</v>
       </c>
       <c r="G81" t="n">
-        <v>0.523749874470906</v>
+        <v>0.42937114178507</v>
       </c>
     </row>
     <row r="82">
@@ -2440,19 +2440,19 @@
         <v>22</v>
       </c>
       <c r="C82" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D82" t="n">
-        <v>0.309901976794455</v>
+        <v>0.322088522772133</v>
       </c>
       <c r="E82" t="n">
-        <v>2.19680517518906</v>
+        <v>2.26513294445982</v>
       </c>
       <c r="F82" t="n">
-        <v>2.23459326267259</v>
+        <v>2.3074771256713</v>
       </c>
       <c r="G82" t="n">
-        <v>0.030236958345378</v>
+        <v>0.0255794074942179</v>
       </c>
     </row>
     <row r="83">
@@ -2463,19 +2463,19 @@
         <v>23</v>
       </c>
       <c r="C83" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D83" t="n">
-        <v>0.146803880356956</v>
+        <v>0.165876552660282</v>
       </c>
       <c r="E83" t="n">
-        <v>0.991957809540855</v>
+        <v>1.11056212320094</v>
       </c>
       <c r="F83" t="n">
-        <v>0.995576826725531</v>
+        <v>1.11575769442194</v>
       </c>
       <c r="G83" t="n">
-        <v>0.324779326138262</v>
+        <v>0.270582570439218</v>
       </c>
     </row>
     <row r="84">
@@ -2486,19 +2486,19 @@
         <v>24</v>
       </c>
       <c r="C84" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1082758324189</v>
+        <v>0.134326488244453</v>
       </c>
       <c r="E84" t="n">
-        <v>0.652211780886184</v>
+        <v>0.799518311526941</v>
       </c>
       <c r="F84" t="n">
-        <v>0.653496975055383</v>
+        <v>0.80195422878682</v>
       </c>
       <c r="G84" t="n">
-        <v>0.517588456984927</v>
+        <v>0.427991065622651</v>
       </c>
     </row>
     <row r="85">
@@ -2509,19 +2509,19 @@
         <v>25</v>
       </c>
       <c r="C85" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D85" t="n">
-        <v>0.151946646955788</v>
+        <v>0.173362057006438</v>
       </c>
       <c r="E85" t="n">
-        <v>0.968494893715691</v>
+        <v>1.09369167193879</v>
       </c>
       <c r="F85" t="n">
-        <v>0.972284463863898</v>
+        <v>1.09929098618498</v>
       </c>
       <c r="G85" t="n">
-        <v>0.336752213123927</v>
+        <v>0.278381025619608</v>
       </c>
     </row>
     <row r="86">
@@ -2532,19 +2532,19 @@
         <v>26</v>
       </c>
       <c r="C86" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D86" t="n">
-        <v>0.231551518322556</v>
+        <v>0.250810516603034</v>
       </c>
       <c r="E86" t="n">
-        <v>1.35473023423894</v>
+        <v>1.44972474801758</v>
       </c>
       <c r="F86" t="n">
-        <v>1.36732241250437</v>
+        <v>1.46564615710996</v>
       </c>
       <c r="G86" t="n">
-        <v>0.180765990050882</v>
+        <v>0.152502577010383</v>
       </c>
     </row>
     <row r="87">
@@ -2555,19 +2555,19 @@
         <v>27</v>
       </c>
       <c r="C87" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D87" t="n">
-        <v>0.166675810283669</v>
+        <v>0.187128359692306</v>
       </c>
       <c r="E87" t="n">
-        <v>1.06407811880499</v>
+        <v>1.18255067764645</v>
       </c>
       <c r="F87" t="n">
-        <v>1.0691052931216</v>
+        <v>1.18963049444522</v>
       </c>
       <c r="G87" t="n">
-        <v>0.291431683587261</v>
+        <v>0.241383823285957</v>
       </c>
     </row>
     <row r="88">
@@ -2581,16 +2581,16 @@
         <v>29</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3023850948155</v>
+        <v>0.30228543832845</v>
       </c>
       <c r="E88" t="n">
-        <v>1.62194081831099</v>
+        <v>1.62137089307828</v>
       </c>
       <c r="F88" t="n">
-        <v>1.64840786488971</v>
+        <v>1.6478099586305</v>
       </c>
       <c r="G88" t="n">
-        <v>0.11085849484497</v>
+        <v>0.110982011874532</v>
       </c>
     </row>
     <row r="89">
@@ -2601,19 +2601,19 @@
         <v>29</v>
       </c>
       <c r="C89" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D89" t="n">
-        <v>0.188419167071727</v>
+        <v>0.20396260084184</v>
       </c>
       <c r="E89" t="n">
-        <v>1.17553920437024</v>
+        <v>1.25830274606991</v>
       </c>
       <c r="F89" t="n">
-        <v>1.18267703337932</v>
+        <v>1.26729630615763</v>
       </c>
       <c r="G89" t="n">
-        <v>0.244284376584446</v>
+        <v>0.212967842044592</v>
       </c>
     </row>
     <row r="90">
@@ -2624,19 +2624,19 @@
         <v>30</v>
       </c>
       <c r="C90" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D90" t="n">
-        <v>0.345304111173864</v>
+        <v>0.359243701398886</v>
       </c>
       <c r="E90" t="n">
-        <v>2.1904165813151</v>
+        <v>2.25610358068492</v>
       </c>
       <c r="F90" t="n">
-        <v>2.23806435048675</v>
+        <v>2.3096453917963</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0313205833231369</v>
+        <v>0.0267544481444679</v>
       </c>
     </row>
     <row r="91">
@@ -2647,19 +2647,19 @@
         <v>31</v>
       </c>
       <c r="C91" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D91" t="n">
-        <v>0.076632127481052</v>
+        <v>0.0973187854738855</v>
       </c>
       <c r="E91" t="n">
-        <v>0.51507377671348</v>
+        <v>0.647589410204647</v>
       </c>
       <c r="F91" t="n">
-        <v>0.515580035501493</v>
+        <v>0.64861861607017</v>
       </c>
       <c r="G91" t="n">
-        <v>0.608671645057046</v>
+        <v>0.519955985148529</v>
       </c>
     </row>
     <row r="92">
@@ -2670,19 +2670,19 @@
         <v>32</v>
       </c>
       <c r="C92" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.0972446011338929</v>
+        <v>-0.107076356627266</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.616978610216961</v>
+        <v>-0.671264952223528</v>
       </c>
       <c r="F92" t="n">
-        <v>0.617957662150115</v>
+        <v>0.672558304832926</v>
       </c>
       <c r="G92" t="n">
-        <v>0.540105950858884</v>
+        <v>0.505193900429673</v>
       </c>
     </row>
     <row r="93">
@@ -2693,19 +2693,19 @@
         <v>33</v>
       </c>
       <c r="C93" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0927078097440144</v>
+        <v>0.108517208838384</v>
       </c>
       <c r="E93" t="n">
-        <v>0.550046261515257</v>
+        <v>0.635260108165924</v>
       </c>
       <c r="F93" t="n">
-        <v>0.550839065937506</v>
+        <v>0.636517533828726</v>
       </c>
       <c r="G93" t="n">
-        <v>0.585243239459585</v>
+        <v>0.52870149445592</v>
       </c>
     </row>
     <row r="94">
@@ -2716,19 +2716,19 @@
         <v>34</v>
       </c>
       <c r="C94" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0288976141659125</v>
+        <v>0.0178822104430486</v>
       </c>
       <c r="E94" t="n">
-        <v>0.171008202944872</v>
+        <v>0.104281425291981</v>
       </c>
       <c r="F94" t="n">
-        <v>0.171032017895104</v>
+        <v>0.104286984304511</v>
       </c>
       <c r="G94" t="n">
-        <v>0.865183550820137</v>
+        <v>0.917554377277114</v>
       </c>
     </row>
     <row r="95">
@@ -2739,19 +2739,19 @@
         <v>35</v>
       </c>
       <c r="C95" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D95" t="n">
-        <v>0.043289273042238</v>
+        <v>0.0505498048913649</v>
       </c>
       <c r="E95" t="n">
-        <v>0.270510483404571</v>
+        <v>0.311875749951435</v>
       </c>
       <c r="F95" t="n">
-        <v>0.27059508473396</v>
+        <v>0.312008815477937</v>
       </c>
       <c r="G95" t="n">
-        <v>0.7881294292323</v>
+        <v>0.756739444461517</v>
       </c>
     </row>
     <row r="96">
@@ -2762,19 +2762,19 @@
         <v>36</v>
       </c>
       <c r="C96" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0560089818436264</v>
+        <v>0.0466923534650569</v>
       </c>
       <c r="E96" t="n">
-        <v>0.34562426326547</v>
+        <v>0.284225171952925</v>
       </c>
       <c r="F96" t="n">
-        <v>0.345805374788817</v>
+        <v>0.284328610413843</v>
       </c>
       <c r="G96" t="n">
-        <v>0.731396206802921</v>
+        <v>0.777743810677376</v>
       </c>
     </row>
     <row r="97">
@@ -2785,19 +2785,19 @@
         <v>37</v>
       </c>
       <c r="C97" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D97" t="n">
-        <v>0.183802372848982</v>
+        <v>0.189740056448898</v>
       </c>
       <c r="E97" t="n">
-        <v>1.05169510689127</v>
+        <v>1.06938660441178</v>
       </c>
       <c r="F97" t="n">
-        <v>1.05776413093444</v>
+        <v>1.07597367464547</v>
       </c>
       <c r="G97" t="n">
-        <v>0.298082978158248</v>
+        <v>0.290242002607158</v>
       </c>
     </row>
     <row r="98">
@@ -2808,19 +2808,19 @@
         <v>38</v>
       </c>
       <c r="C98" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0931619955043574</v>
+        <v>0.0898839006509042</v>
       </c>
       <c r="E98" t="n">
-        <v>0.511753235625744</v>
+        <v>0.485349511409764</v>
       </c>
       <c r="F98" t="n">
-        <v>0.512498137124188</v>
+        <v>0.48600685272114</v>
       </c>
       <c r="G98" t="n">
-        <v>0.612055347699261</v>
+        <v>0.6306145865181</v>
       </c>
     </row>
     <row r="99">
@@ -2831,19 +2831,19 @@
         <v>39</v>
       </c>
       <c r="C99" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D99" t="n">
-        <v>0.190647724585919</v>
+        <v>0.200568781320813</v>
       </c>
       <c r="E99" t="n">
-        <v>1.20534230689974</v>
+        <v>1.25338012368299</v>
       </c>
       <c r="F99" t="n">
-        <v>1.21283994090951</v>
+        <v>1.26203401086674</v>
       </c>
       <c r="G99" t="n">
-        <v>0.232486524398927</v>
+        <v>0.21462781944376</v>
       </c>
     </row>
     <row r="100">
@@ -2854,19 +2854,19 @@
         <v>40</v>
       </c>
       <c r="C100" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D100" t="n">
-        <v>0.237770269730923</v>
+        <v>0.230859063543075</v>
       </c>
       <c r="E100" t="n">
-        <v>1.51384645771706</v>
+        <v>1.44923340536363</v>
       </c>
       <c r="F100" t="n">
-        <v>1.52871627212293</v>
+        <v>1.46262031294227</v>
       </c>
       <c r="G100" t="n">
-        <v>0.134405847133485</v>
+        <v>0.151793560389817</v>
       </c>
     </row>
     <row r="101">
@@ -2880,16 +2880,16 @@
         <v>28</v>
       </c>
       <c r="D101" t="n">
-        <v>0.242711247015793</v>
+        <v>0.242830120758631</v>
       </c>
       <c r="E101" t="n">
-        <v>1.26278782810667</v>
+        <v>1.26343192943144</v>
       </c>
       <c r="F101" t="n">
-        <v>1.27573569642744</v>
+        <v>1.27639966111617</v>
       </c>
       <c r="G101" t="n">
-        <v>0.21332927268776</v>
+        <v>0.213098194567549</v>
       </c>
     </row>
     <row r="102">
@@ -2903,16 +2903,16 @@
         <v>28</v>
       </c>
       <c r="D102" t="n">
-        <v>0.215521830831675</v>
+        <v>0.215640855447361</v>
       </c>
       <c r="E102" t="n">
-        <v>1.11645584279272</v>
+        <v>1.1170923327009</v>
       </c>
       <c r="F102" t="n">
-        <v>1.12539797376906</v>
+        <v>1.12604979057275</v>
       </c>
       <c r="G102" t="n">
-        <v>0.270702224522392</v>
+        <v>0.270431285270296</v>
       </c>
     </row>
     <row r="103">
@@ -2923,19 +2923,19 @@
         <v>43</v>
       </c>
       <c r="C103" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D103" t="n">
-        <v>0.105997835683631</v>
+        <v>0.111400760600555</v>
       </c>
       <c r="E103" t="n">
-        <v>0.655878328535627</v>
+        <v>0.680448567012642</v>
       </c>
       <c r="F103" t="n">
-        <v>0.657116500064471</v>
+        <v>0.68186862038143</v>
       </c>
       <c r="G103" t="n">
-        <v>0.515066521882684</v>
+        <v>0.499568413763007</v>
       </c>
     </row>
     <row r="104">
@@ -2946,19 +2946,19 @@
         <v>44</v>
       </c>
       <c r="C104" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D104" t="n">
-        <v>0.307543196387699</v>
+        <v>0.314439396796278</v>
       </c>
       <c r="E104" t="n">
-        <v>1.93328251147345</v>
+        <v>1.95278591129013</v>
       </c>
       <c r="F104" t="n">
-        <v>1.96599595459203</v>
+        <v>1.98744443290065</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0568365056290313</v>
+        <v>0.0545216395490505</v>
       </c>
     </row>
     <row r="105">
@@ -2969,19 +2969,19 @@
         <v>45</v>
       </c>
       <c r="C105" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D105" t="n">
-        <v>0.141483750347513</v>
+        <v>0.121710002622681</v>
       </c>
       <c r="E105" t="n">
-        <v>0.753717988711956</v>
+        <v>0.635574543227781</v>
       </c>
       <c r="F105" t="n">
-        <v>0.756269267500813</v>
+        <v>0.637160565720553</v>
       </c>
       <c r="G105" t="n">
-        <v>0.455804032534537</v>
+        <v>0.529386390338643</v>
       </c>
     </row>
     <row r="106">
@@ -2992,19 +2992,19 @@
         <v>46</v>
       </c>
       <c r="C106" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.0349991308069497</v>
+        <v>-0.0530611459996863</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.201136853141344</v>
+        <v>-0.300441343961149</v>
       </c>
       <c r="F106" t="n">
-        <v>0.201177952626737</v>
+        <v>0.300582610437214</v>
       </c>
       <c r="G106" t="n">
-        <v>0.841794329975384</v>
+        <v>0.765677064592231</v>
       </c>
     </row>
     <row r="107">
@@ -3015,19 +3015,19 @@
         <v>47</v>
       </c>
       <c r="C107" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D107" t="n">
-        <v>0.287434638990142</v>
+        <v>0.282489069123737</v>
       </c>
       <c r="E107" t="n">
-        <v>1.59275733181372</v>
+        <v>1.53657264952927</v>
       </c>
       <c r="F107" t="n">
-        <v>1.6160811132631</v>
+        <v>1.55825872124271</v>
       </c>
       <c r="G107" t="n">
-        <v>0.116905175029004</v>
+        <v>0.13040433561928</v>
       </c>
     </row>
     <row r="108">
@@ -3038,19 +3038,19 @@
         <v>48</v>
       </c>
       <c r="C108" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.224029884683939</v>
+        <v>-0.224850602033692</v>
       </c>
       <c r="E108" t="n">
-        <v>-1.22725178399496</v>
+        <v>-1.21047984227341</v>
       </c>
       <c r="F108" t="n">
-        <v>1.23790251647138</v>
+        <v>1.22106505720061</v>
       </c>
       <c r="G108" t="n">
-        <v>0.225680918153751</v>
+        <v>0.232244078850662</v>
       </c>
     </row>
     <row r="109">
@@ -3064,16 +3064,16 @@
         <v>15</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.0948275695153737</v>
+        <v>-0.0939162196481799</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.342936065120608</v>
+        <v>-0.339620618660005</v>
       </c>
       <c r="F109" t="n">
-        <v>0.343453363740507</v>
+        <v>0.340123054030019</v>
       </c>
       <c r="G109" t="n">
-        <v>0.736748383068612</v>
+        <v>0.739196795681053</v>
       </c>
     </row>
     <row r="110">
@@ -3087,16 +3087,16 @@
         <v>24</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.0845390147356955</v>
+        <v>-0.0846215963520797</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.397471828281277</v>
+        <v>-0.397861961341308</v>
       </c>
       <c r="F110" t="n">
-        <v>0.397947712233939</v>
+        <v>0.398339248298652</v>
       </c>
       <c r="G110" t="n">
-        <v>0.694504034739044</v>
+        <v>0.694219640387759</v>
       </c>
     </row>
     <row r="111">
@@ -3107,19 +3107,19 @@
         <v>51</v>
       </c>
       <c r="C111" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0751753365721305</v>
+        <v>0.117621978654485</v>
       </c>
       <c r="E111" t="n">
-        <v>0.391360858202831</v>
+        <v>0.602545817321577</v>
       </c>
       <c r="F111" t="n">
-        <v>0.391730976307221</v>
+        <v>0.60394911189921</v>
       </c>
       <c r="G111" t="n">
-        <v>0.698331795398653</v>
+        <v>0.551111238148757</v>
       </c>
     </row>
     <row r="112">
@@ -3130,19 +3130,19 @@
         <v>52</v>
       </c>
       <c r="C112" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D112" t="n">
-        <v>0.134114670548773</v>
+        <v>0.129703106387817</v>
       </c>
       <c r="E112" t="n">
-        <v>0.775099803420815</v>
+        <v>0.737867988135936</v>
       </c>
       <c r="F112" t="n">
-        <v>0.777453784716137</v>
+        <v>0.739962120971685</v>
       </c>
       <c r="G112" t="n">
-        <v>0.442429229892928</v>
+        <v>0.464717523720147</v>
       </c>
     </row>
     <row r="113">
@@ -3153,19 +3153,19 @@
         <v>53</v>
       </c>
       <c r="C113" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D113" t="n">
-        <v>0.0465190505942828</v>
+        <v>0.0673102600041457</v>
       </c>
       <c r="E113" t="n">
-        <v>0.241894666719952</v>
+        <v>0.343736076276016</v>
       </c>
       <c r="F113" t="n">
-        <v>0.241982046495314</v>
+        <v>0.343996481341034</v>
       </c>
       <c r="G113" t="n">
-        <v>0.810622616942327</v>
+        <v>0.733615532981247</v>
       </c>
     </row>
     <row r="114">
@@ -3176,19 +3176,19 @@
         <v>54</v>
       </c>
       <c r="C114" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D114" t="n">
-        <v>0.100142263574093</v>
+        <v>0.0909245929701823</v>
       </c>
       <c r="E114" t="n">
-        <v>0.522104461047566</v>
+        <v>0.464910292056702</v>
       </c>
       <c r="F114" t="n">
-        <v>0.522983435854419</v>
+        <v>0.465554703730267</v>
       </c>
       <c r="G114" t="n">
-        <v>0.605251500525445</v>
+        <v>0.645410540768032</v>
       </c>
     </row>
     <row r="115">
@@ -3202,16 +3202,16 @@
         <v>15</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.0315218014048753</v>
+        <v>-0.0307007941347251</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.113691136655503</v>
+        <v>-0.110728084702308</v>
       </c>
       <c r="F115" t="n">
-        <v>0.11370997777974</v>
+        <v>0.110745490712789</v>
       </c>
       <c r="G115" t="n">
-        <v>0.91120503524867</v>
+        <v>0.91350966876847</v>
       </c>
     </row>
     <row r="116">
@@ -3225,16 +3225,16 @@
         <v>23</v>
       </c>
       <c r="D116" t="n">
-        <v>0.268483458666792</v>
+        <v>0.269466190003676</v>
       </c>
       <c r="E116" t="n">
-        <v>1.26125659354814</v>
+        <v>1.26611125737826</v>
       </c>
       <c r="F116" t="n">
-        <v>1.27724056018467</v>
+        <v>1.2822809778035</v>
       </c>
       <c r="G116" t="n">
-        <v>0.215458831483145</v>
+        <v>0.213719120379512</v>
       </c>
     </row>
     <row r="117">
@@ -3245,19 +3245,19 @@
         <v>57</v>
       </c>
       <c r="C117" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D117" t="n">
-        <v>0.00604451117906005</v>
+        <v>-0.0025727128839635</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0372613231523892</v>
+        <v>-0.0156492360585065</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0372615500556642</v>
+        <v>0.0156492533219169</v>
       </c>
       <c r="G117" t="n">
-        <v>0.970471527841125</v>
+        <v>0.987598294563283</v>
       </c>
     </row>
     <row r="118">
@@ -3268,19 +3268,19 @@
         <v>58</v>
       </c>
       <c r="C118" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D118" t="n">
-        <v>0.127321948285432</v>
+        <v>0.127098383599548</v>
       </c>
       <c r="E118" t="n">
-        <v>0.778695300529868</v>
+        <v>0.766736860875059</v>
       </c>
       <c r="F118" t="n">
-        <v>0.780823956841013</v>
+        <v>0.768825386816895</v>
       </c>
       <c r="G118" t="n">
-        <v>0.439873409094492</v>
+        <v>0.447011766186465</v>
       </c>
     </row>
     <row r="119">
@@ -3291,19 +3291,19 @@
         <v>59</v>
       </c>
       <c r="C119" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.0805795195608697</v>
+        <v>-0.0932920600996489</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.484527628174498</v>
+        <v>-0.553532889135217</v>
       </c>
       <c r="F119" t="n">
-        <v>0.485054425418101</v>
+        <v>0.554340870027562</v>
       </c>
       <c r="G119" t="n">
-        <v>0.630576436364006</v>
+        <v>0.582870641058271</v>
       </c>
     </row>
     <row r="120">
@@ -3314,19 +3314,19 @@
         <v>60</v>
       </c>
       <c r="C120" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0502107006974417</v>
+        <v>0.0569551003037848</v>
       </c>
       <c r="E120" t="n">
-        <v>0.297300522364663</v>
+        <v>0.332462251136401</v>
       </c>
       <c r="F120" t="n">
-        <v>0.297425669974464</v>
+        <v>0.332642414901262</v>
       </c>
       <c r="G120" t="n">
-        <v>0.767899794895122</v>
+        <v>0.741446571968704</v>
       </c>
     </row>
     <row r="121">
@@ -3337,19 +3337,19 @@
         <v>61</v>
       </c>
       <c r="C121" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D121" t="n">
-        <v>0.00187530039268866</v>
+        <v>-0.00753378688408188</v>
       </c>
       <c r="E121" t="n">
-        <v>0.0128564268352372</v>
+        <v>-0.0510975954165172</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0128564343707326</v>
+        <v>0.0510980788019297</v>
       </c>
       <c r="G121" t="n">
-        <v>0.98979675118329</v>
+        <v>0.959468613481159</v>
       </c>
     </row>
     <row r="122">
@@ -3360,19 +3360,19 @@
         <v>62</v>
       </c>
       <c r="C122" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.13171414277013</v>
+        <v>-0.11329117514991</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.816685342547616</v>
+        <v>-0.692094503996116</v>
       </c>
       <c r="F122" t="n">
-        <v>0.819076513161073</v>
+        <v>0.693588757686949</v>
       </c>
       <c r="G122" t="n">
-        <v>0.417850236978656</v>
+        <v>0.49227172457046</v>
       </c>
     </row>
     <row r="123">
@@ -3383,19 +3383,19 @@
         <v>63</v>
       </c>
       <c r="C123" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0345621776378312</v>
+        <v>0.0530682415418155</v>
       </c>
       <c r="E123" t="n">
-        <v>0.213140467419391</v>
+        <v>0.323105052927633</v>
       </c>
       <c r="F123" t="n">
-        <v>0.21318293806417</v>
+        <v>0.323257016517279</v>
       </c>
       <c r="G123" t="n">
-        <v>0.832323890833338</v>
+        <v>0.748320551496533</v>
       </c>
     </row>
     <row r="124">
@@ -3409,16 +3409,16 @@
         <v>40</v>
       </c>
       <c r="D124" t="n">
-        <v>0.0369135978314559</v>
+        <v>0.0382380454731278</v>
       </c>
       <c r="E124" t="n">
-        <v>0.227654138521104</v>
+        <v>0.235830127336601</v>
       </c>
       <c r="F124" t="n">
-        <v>0.227705889839464</v>
+        <v>0.235887657391777</v>
       </c>
       <c r="G124" t="n">
-        <v>0.821095664167239</v>
+        <v>0.814786623654813</v>
       </c>
     </row>
     <row r="125">
@@ -3432,16 +3432,16 @@
         <v>40</v>
       </c>
       <c r="D125" t="n">
-        <v>0.100445672199063</v>
+        <v>0.102134202431095</v>
       </c>
       <c r="E125" t="n">
-        <v>0.621283806195153</v>
+        <v>0.631800505876872</v>
       </c>
       <c r="F125" t="n">
-        <v>0.622336145578712</v>
+        <v>0.632907214161169</v>
       </c>
       <c r="G125" t="n">
-        <v>0.537437565105124</v>
+        <v>0.530584804311273</v>
       </c>
     </row>
     <row r="126">
@@ -3452,19 +3452,19 @@
         <v>66</v>
       </c>
       <c r="C126" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0378340960802574</v>
+        <v>0.0610346749929765</v>
       </c>
       <c r="E126" t="n">
-        <v>0.256725865100911</v>
+        <v>0.409942597176446</v>
       </c>
       <c r="F126" t="n">
-        <v>0.256787175043355</v>
+        <v>0.41019780058702</v>
       </c>
       <c r="G126" t="n">
-        <v>0.798488156101064</v>
+        <v>0.683607319739358</v>
       </c>
     </row>
     <row r="127">
@@ -3475,19 +3475,19 @@
         <v>67</v>
       </c>
       <c r="C127" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.0617844568534664</v>
+        <v>-0.10520512787339</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.424113104660977</v>
+        <v>-0.71618601470123</v>
       </c>
       <c r="F127" t="n">
-        <v>0.424383674305253</v>
+        <v>0.717517727435819</v>
       </c>
       <c r="G127" t="n">
-        <v>0.673222368024878</v>
+        <v>0.476682797654696</v>
       </c>
     </row>
     <row r="128">
@@ -3498,19 +3498,19 @@
         <v>68</v>
       </c>
       <c r="C128" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D128" t="n">
-        <v>0.0440141905939709</v>
+        <v>0.0281250616347453</v>
       </c>
       <c r="E128" t="n">
-        <v>0.301941167462205</v>
+        <v>0.190803769227342</v>
       </c>
       <c r="F128" t="n">
-        <v>0.30203879222746</v>
+        <v>0.190828938400747</v>
       </c>
       <c r="G128" t="n">
-        <v>0.763955033588546</v>
+        <v>0.849499363563012</v>
       </c>
     </row>
     <row r="129">
@@ -3521,19 +3521,19 @@
         <v>69</v>
       </c>
       <c r="C129" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.0448331931011325</v>
+        <v>-0.0773754882097898</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.307567068600726</v>
+        <v>-0.525837164066747</v>
       </c>
       <c r="F129" t="n">
-        <v>0.307670253013609</v>
+        <v>0.526364121184181</v>
       </c>
       <c r="G129" t="n">
-        <v>0.759692568752437</v>
+        <v>0.601164143545479</v>
       </c>
     </row>
     <row r="130">
@@ -3544,19 +3544,19 @@
         <v>70</v>
       </c>
       <c r="C130" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D130" t="n">
-        <v>0.109319658558897</v>
+        <v>0.0838009249758226</v>
       </c>
       <c r="E130" t="n">
-        <v>0.752464949394588</v>
+        <v>0.569701627322828</v>
       </c>
       <c r="F130" t="n">
-        <v>0.753976669214941</v>
+        <v>0.570371799676573</v>
       </c>
       <c r="G130" t="n">
-        <v>0.454624201567905</v>
+        <v>0.57120123440895</v>
       </c>
     </row>
     <row r="131">
@@ -3567,19 +3567,19 @@
         <v>71</v>
       </c>
       <c r="C131" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.0479433437199535</v>
+        <v>-0.0891067293596616</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.328935185813013</v>
+        <v>-0.605958423977745</v>
       </c>
       <c r="F131" t="n">
-        <v>0.3290614068886</v>
+        <v>0.606764902362216</v>
       </c>
       <c r="G131" t="n">
-        <v>0.743571144451562</v>
+        <v>0.546990177574743</v>
       </c>
     </row>
     <row r="132">
@@ -3590,19 +3590,19 @@
         <v>72</v>
       </c>
       <c r="C132" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.00154802740505567</v>
+        <v>-0.0430546413177916</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.0106127496784473</v>
+        <v>-0.292191419342718</v>
       </c>
       <c r="F132" t="n">
-        <v>0.010612753917167</v>
+        <v>0.29228181209176</v>
       </c>
       <c r="G132" t="n">
-        <v>0.991577327254295</v>
+        <v>0.771385429419899</v>
       </c>
     </row>
     <row r="133">
@@ -3613,19 +3613,19 @@
         <v>73</v>
       </c>
       <c r="C133" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.0378624912519765</v>
+        <v>-0.0808369982997949</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.259696307270207</v>
+        <v>-0.549462132192646</v>
       </c>
       <c r="F133" t="n">
-        <v>0.259758419822262</v>
+        <v>0.550063370629314</v>
       </c>
       <c r="G133" t="n">
-        <v>0.796184645601461</v>
+        <v>0.584937094366457</v>
       </c>
     </row>
     <row r="134">
@@ -3636,19 +3636,19 @@
         <v>8</v>
       </c>
       <c r="C134" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.130175216149773</v>
+        <v>-0.101471980363457</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.897529153653715</v>
+        <v>-0.690593243873313</v>
       </c>
       <c r="F134" t="n">
-        <v>0.900095225178548</v>
+        <v>0.691787185310217</v>
       </c>
       <c r="G134" t="n">
-        <v>0.372658483475695</v>
+        <v>0.492548097397089</v>
       </c>
     </row>
     <row r="135">
@@ -3659,19 +3659,19 @@
         <v>9</v>
       </c>
       <c r="C135" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D135" t="n">
-        <v>0.169444011066943</v>
+        <v>0.180769792716834</v>
       </c>
       <c r="E135" t="n">
-        <v>0.838186897308406</v>
+        <v>0.876574277593589</v>
       </c>
       <c r="F135" t="n">
-        <v>0.842282291861792</v>
+        <v>0.881463192701652</v>
       </c>
       <c r="G135" t="n">
-        <v>0.407945425541102</v>
+        <v>0.38718623181786</v>
       </c>
     </row>
     <row r="136">
@@ -3682,19 +3682,19 @@
         <v>10</v>
       </c>
       <c r="C136" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D136" t="n">
-        <v>0.117517220307221</v>
+        <v>0.0875464879156639</v>
       </c>
       <c r="E136" t="n">
-        <v>0.578386893550803</v>
+        <v>0.420935818403246</v>
       </c>
       <c r="F136" t="n">
-        <v>0.579731500989833</v>
+        <v>0.421476492850436</v>
       </c>
       <c r="G136" t="n">
-        <v>0.567498628768861</v>
+        <v>0.677320191500195</v>
       </c>
     </row>
     <row r="137">
@@ -3705,19 +3705,19 @@
         <v>11</v>
       </c>
       <c r="C137" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.117517220307221</v>
+        <v>-0.0875464879156639</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.578386893550803</v>
+        <v>-0.420935818403246</v>
       </c>
       <c r="F137" t="n">
-        <v>0.579731500989833</v>
+        <v>0.421476492850436</v>
       </c>
       <c r="G137" t="n">
-        <v>0.567498628768861</v>
+        <v>0.677320191500195</v>
       </c>
     </row>
     <row r="138">
@@ -3728,19 +3728,19 @@
         <v>12</v>
       </c>
       <c r="C138" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D138" t="n">
-        <v>0.117517220307221</v>
+        <v>0.0875464879156639</v>
       </c>
       <c r="E138" t="n">
-        <v>0.578386893550803</v>
+        <v>0.420935818403246</v>
       </c>
       <c r="F138" t="n">
-        <v>0.579731500989833</v>
+        <v>0.421476492850436</v>
       </c>
       <c r="G138" t="n">
-        <v>0.567498628768861</v>
+        <v>0.677320191500195</v>
       </c>
     </row>
     <row r="139">
@@ -3751,19 +3751,19 @@
         <v>13</v>
       </c>
       <c r="C139" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.0197959873374666</v>
+        <v>-0.0580617301867538</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.135732183805971</v>
+        <v>-0.394237225328822</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1357410514431</v>
+        <v>0.394459268374209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.892605716067686</v>
+        <v>0.695064937752</v>
       </c>
     </row>
     <row r="140">
@@ -3774,19 +3774,19 @@
         <v>14</v>
       </c>
       <c r="C140" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.0903745173058739</v>
+        <v>-0.124401717267582</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.621271598095088</v>
+        <v>-0.848126844040808</v>
       </c>
       <c r="F140" t="n">
-        <v>0.622122292776916</v>
+        <v>0.850338985527642</v>
       </c>
       <c r="G140" t="n">
-        <v>0.536867981071466</v>
+        <v>0.399541167557248</v>
       </c>
     </row>
     <row r="141">
@@ -3797,19 +3797,19 @@
         <v>15</v>
       </c>
       <c r="C141" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.0252827023796898</v>
+        <v>-0.063331587447926</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.173366420653087</v>
+        <v>-0.430111383916872</v>
       </c>
       <c r="F141" t="n">
-        <v>0.173384898855762</v>
+        <v>0.430399734649051</v>
       </c>
       <c r="G141" t="n">
-        <v>0.863093485158087</v>
+        <v>0.668914770644151</v>
       </c>
     </row>
     <row r="142">
@@ -3820,19 +3820,19 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D142" t="n">
-        <v>0.0188675692702203</v>
+        <v>-0.00409811049288621</v>
       </c>
       <c r="E142" t="n">
-        <v>0.129364890184087</v>
+        <v>-0.0277948932712931</v>
       </c>
       <c r="F142" t="n">
-        <v>0.129372567473209</v>
+        <v>0.0277949710724968</v>
       </c>
       <c r="G142" t="n">
-        <v>0.897614928715637</v>
+        <v>0.977945914931329</v>
       </c>
     </row>
     <row r="143">
@@ -3843,19 +3843,19 @@
         <v>17</v>
       </c>
       <c r="C143" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D143" t="n">
-        <v>0.0116034330046273</v>
+        <v>-0.0109528331336859</v>
       </c>
       <c r="E143" t="n">
-        <v>0.0795526993028782</v>
+        <v>-0.0742886993280238</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0795544846331811</v>
+        <v>0.0742901847908466</v>
       </c>
       <c r="G143" t="n">
-        <v>0.936929365996278</v>
+        <v>0.941101614164067</v>
       </c>
     </row>
     <row r="144">
@@ -3866,19 +3866,19 @@
         <v>18</v>
       </c>
       <c r="C144" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.085419765658926</v>
+        <v>-0.129123679518546</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.587038981933315</v>
+        <v>-0.880675837291347</v>
       </c>
       <c r="F144" t="n">
-        <v>0.587756629028575</v>
+        <v>0.883152719067759</v>
       </c>
       <c r="G144" t="n">
-        <v>0.559509197520105</v>
+        <v>0.381746085550637</v>
       </c>
     </row>
     <row r="145">
@@ -3889,19 +3889,19 @@
         <v>19</v>
       </c>
       <c r="C145" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.186640485411808</v>
+        <v>-0.157955287596299</v>
       </c>
       <c r="E145" t="n">
-        <v>-1.2808710042956</v>
+        <v>-1.06854286205487</v>
       </c>
       <c r="F145" t="n">
-        <v>1.28849849247143</v>
+        <v>1.07306728325759</v>
       </c>
       <c r="G145" t="n">
-        <v>0.204015690858859</v>
+        <v>0.288961794534702</v>
       </c>
     </row>
     <row r="146">
@@ -3912,19 +3912,19 @@
         <v>20</v>
       </c>
       <c r="C146" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D146" t="n">
-        <v>0.0322058488549287</v>
+        <v>0.0998941703684409</v>
       </c>
       <c r="E146" t="n">
-        <v>0.220868559847843</v>
+        <v>0.679782423331082</v>
       </c>
       <c r="F146" t="n">
-        <v>0.220906769679856</v>
+        <v>0.680921148314924</v>
       </c>
       <c r="G146" t="n">
-        <v>0.826121909858242</v>
+        <v>0.499334875418327</v>
       </c>
     </row>
     <row r="147">
@@ -3935,19 +3935,19 @@
         <v>21</v>
       </c>
       <c r="C147" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D147" t="n">
-        <v>0.0767295614121048</v>
+        <v>0.123604508076239</v>
       </c>
       <c r="E147" t="n">
-        <v>0.52706735624259</v>
+        <v>0.842635468298042</v>
       </c>
       <c r="F147" t="n">
-        <v>0.527586727122688</v>
+        <v>0.84480489657586</v>
       </c>
       <c r="G147" t="n">
-        <v>0.600268136833987</v>
+        <v>0.402592381634895</v>
       </c>
     </row>
     <row r="148">
@@ -3958,19 +3958,19 @@
         <v>22</v>
       </c>
       <c r="C148" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D148" t="n">
-        <v>0.147173667216689</v>
+        <v>0.1160431307197</v>
       </c>
       <c r="E148" t="n">
-        <v>1.01635279861435</v>
+        <v>0.790604400647595</v>
       </c>
       <c r="F148" t="n">
-        <v>1.02007981747703</v>
+        <v>0.792396093901202</v>
       </c>
       <c r="G148" t="n">
-        <v>0.312912850797289</v>
+        <v>0.432197494708551</v>
       </c>
     </row>
     <row r="149">
@@ -3981,19 +3981,19 @@
         <v>23</v>
       </c>
       <c r="C149" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.0011541031965517</v>
+        <v>0.00436945589096948</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.00774196303893254</v>
+        <v>0.0289838759124321</v>
       </c>
       <c r="F149" t="n">
-        <v>0.00774196475759108</v>
+        <v>0.0289839681410863</v>
       </c>
       <c r="G149" t="n">
-        <v>0.993857088366317</v>
+        <v>0.977008444700625</v>
       </c>
     </row>
     <row r="150">
@@ -4004,19 +4004,19 @@
         <v>24</v>
       </c>
       <c r="C150" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.0284044881067505</v>
+        <v>0.00467854264948867</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.170472785172188</v>
+        <v>0.0276788335359814</v>
       </c>
       <c r="F150" t="n">
-        <v>0.17049572176729</v>
+        <v>0.0276789345134625</v>
       </c>
       <c r="G150" t="n">
-        <v>0.86557491834019</v>
+        <v>0.978075448753266</v>
       </c>
     </row>
     <row r="151">
@@ -4027,19 +4027,19 @@
         <v>25</v>
       </c>
       <c r="C151" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.120767130100101</v>
+        <v>-0.0926352102185692</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.767544488379773</v>
+        <v>-0.5801700514501</v>
       </c>
       <c r="F151" t="n">
-        <v>0.769429956709352</v>
+        <v>0.581004957241972</v>
       </c>
       <c r="G151" t="n">
-        <v>0.446158123585823</v>
+        <v>0.564579903367881</v>
       </c>
     </row>
     <row r="152">
@@ -4050,19 +4050,19 @@
         <v>26</v>
       </c>
       <c r="C152" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.00462651386823988</v>
+        <v>0.0471912523600133</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.0265774883793705</v>
+        <v>0.267152471822361</v>
       </c>
       <c r="F152" t="n">
-        <v>0.026577583194378</v>
+        <v>0.267251789096774</v>
       </c>
       <c r="G152" t="n">
-        <v>0.978956728137879</v>
+        <v>0.790990233839859</v>
       </c>
     </row>
     <row r="153">
@@ -4073,19 +4073,19 @@
         <v>27</v>
       </c>
       <c r="C153" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D153" t="n">
-        <v>0.111641258415345</v>
+        <v>0.138336418792819</v>
       </c>
       <c r="E153" t="n">
-        <v>0.709036927922375</v>
+        <v>0.869485689300547</v>
       </c>
       <c r="F153" t="n">
-        <v>0.710523097051842</v>
+        <v>0.872297540812194</v>
       </c>
       <c r="G153" t="n">
-        <v>0.481502233702496</v>
+        <v>0.38838494489552</v>
       </c>
     </row>
     <row r="154">
@@ -4099,16 +4099,16 @@
         <v>29</v>
       </c>
       <c r="D154" t="n">
-        <v>0.0935495374945953</v>
+        <v>0.140387374130697</v>
       </c>
       <c r="E154" t="n">
-        <v>0.487523179175183</v>
+        <v>0.734323982906909</v>
       </c>
       <c r="F154" t="n">
-        <v>0.488238765353185</v>
+        <v>0.736770688918353</v>
       </c>
       <c r="G154" t="n">
-        <v>0.629322523426153</v>
+        <v>0.467615958944476</v>
       </c>
     </row>
     <row r="155">
@@ -4119,19 +4119,19 @@
         <v>29</v>
       </c>
       <c r="C155" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D155" t="n">
-        <v>0.153152163024763</v>
+        <v>0.190599050933258</v>
       </c>
       <c r="E155" t="n">
-        <v>0.951580412983621</v>
+        <v>1.17372212844605</v>
       </c>
       <c r="F155" t="n">
-        <v>0.955364133611028</v>
+        <v>1.18101924651157</v>
       </c>
       <c r="G155" t="n">
-        <v>0.345432118809636</v>
+        <v>0.245131273706189</v>
       </c>
     </row>
     <row r="156">
@@ -4142,19 +4142,19 @@
         <v>30</v>
       </c>
       <c r="C156" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.102360129471596</v>
+        <v>-0.03860836114378</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.624820697279923</v>
+        <v>-0.23176536958815</v>
       </c>
       <c r="F156" t="n">
-        <v>0.625920063439322</v>
+        <v>0.231823009629207</v>
       </c>
       <c r="G156" t="n">
-        <v>0.535209726902362</v>
+        <v>0.817988219662733</v>
       </c>
     </row>
     <row r="157">
@@ -4165,19 +4165,19 @@
         <v>31</v>
       </c>
       <c r="C157" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D157" t="n">
-        <v>0.0146728491869374</v>
+        <v>0.0254777544665809</v>
       </c>
       <c r="E157" t="n">
-        <v>0.09843552916622</v>
+        <v>0.169036885313481</v>
       </c>
       <c r="F157" t="n">
-        <v>0.098439061783202</v>
+        <v>0.169055181248954</v>
       </c>
       <c r="G157" t="n">
-        <v>0.92202084803675</v>
+        <v>0.866528043576032</v>
       </c>
     </row>
     <row r="158">
@@ -4188,19 +4188,19 @@
         <v>32</v>
       </c>
       <c r="C158" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.316030270025639</v>
+        <v>-0.318820381942931</v>
       </c>
       <c r="E158" t="n">
-        <v>-2.06958882574934</v>
+        <v>-2.06293185363757</v>
       </c>
       <c r="F158" t="n">
-        <v>2.10672232573751</v>
+        <v>2.10065500746679</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0414614499045388</v>
+        <v>0.0421866108506569</v>
       </c>
     </row>
     <row r="159">
@@ -4211,19 +4211,19 @@
         <v>33</v>
       </c>
       <c r="C159" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.0962429401974535</v>
+        <v>-0.0770187297919413</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.571148750390255</v>
+        <v>-0.449983670671061</v>
       </c>
       <c r="F159" t="n">
-        <v>0.572036377961773</v>
+        <v>0.450430446238246</v>
       </c>
       <c r="G159" t="n">
-        <v>0.570953454116553</v>
+        <v>0.655259340429587</v>
       </c>
     </row>
     <row r="160">
@@ -4234,19 +4234,19 @@
         <v>34</v>
       </c>
       <c r="C160" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.206144221385781</v>
+        <v>-0.214904044241332</v>
       </c>
       <c r="E160" t="n">
-        <v>-1.23729528848881</v>
+        <v>-1.27293886830801</v>
       </c>
       <c r="F160" t="n">
-        <v>1.24633491599734</v>
+        <v>1.28307395102926</v>
       </c>
       <c r="G160" t="n">
-        <v>0.22091906132045</v>
+        <v>0.208143646644058</v>
       </c>
     </row>
     <row r="161">
@@ -4257,19 +4257,19 @@
         <v>35</v>
       </c>
       <c r="C161" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.188910480602509</v>
+        <v>-0.174754823507642</v>
       </c>
       <c r="E161" t="n">
-        <v>-1.19408787771247</v>
+        <v>-1.08843275964421</v>
       </c>
       <c r="F161" t="n">
-        <v>1.20137719525862</v>
+        <v>1.09409706840898</v>
       </c>
       <c r="G161" t="n">
-        <v>0.236850085563816</v>
+        <v>0.280799419329599</v>
       </c>
     </row>
     <row r="162">
@@ -4280,19 +4280,19 @@
         <v>36</v>
       </c>
       <c r="C162" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.288095115691869</v>
+        <v>-0.297137867513821</v>
       </c>
       <c r="E162" t="n">
-        <v>-1.82767304822627</v>
+        <v>-1.8636207146843</v>
       </c>
       <c r="F162" t="n">
-        <v>1.85456790944853</v>
+        <v>1.89291329858427</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0714302180071337</v>
+        <v>0.0662116631074783</v>
       </c>
     </row>
     <row r="163">
@@ -4303,19 +4303,19 @@
         <v>37</v>
       </c>
       <c r="C163" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.0255516718801848</v>
+        <v>-0.00134243008494319</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.144573552579602</v>
+        <v>-0.00747433887642121</v>
       </c>
       <c r="F163" t="n">
-        <v>0.144589291665794</v>
+        <v>0.00747434112136492</v>
       </c>
       <c r="G163" t="n">
-        <v>0.88594197592135</v>
+        <v>0.994084287847287</v>
       </c>
     </row>
     <row r="164">
@@ -4326,19 +4326,19 @@
         <v>38</v>
       </c>
       <c r="C164" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.104722993911712</v>
+        <v>-0.108261061783205</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.575702208182925</v>
+        <v>-0.585297502438232</v>
       </c>
       <c r="F164" t="n">
-        <v>0.576762831270863</v>
+        <v>0.5864505235891</v>
       </c>
       <c r="G164" t="n">
-        <v>0.568402615545755</v>
+        <v>0.562110339788904</v>
       </c>
     </row>
     <row r="165">
@@ -4349,19 +4349,19 @@
         <v>39</v>
       </c>
       <c r="C165" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D165" t="n">
-        <v>0.120103236008914</v>
+        <v>0.137439097055959</v>
       </c>
       <c r="E165" t="n">
-        <v>0.753682417393867</v>
+        <v>0.852627377729026</v>
       </c>
       <c r="F165" t="n">
-        <v>0.75551332135627</v>
+        <v>0.855348564721357</v>
       </c>
       <c r="G165" t="n">
-        <v>0.454480061679517</v>
+        <v>0.397719342604486</v>
       </c>
     </row>
     <row r="166">
@@ -4372,19 +4372,19 @@
         <v>40</v>
       </c>
       <c r="C166" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.0704609217010757</v>
+        <v>-0.0664076595380093</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.440758700876051</v>
+        <v>-0.409967666073871</v>
       </c>
       <c r="F166" t="n">
-        <v>0.44112471259522</v>
+        <v>0.410269946491058</v>
       </c>
       <c r="G166" t="n">
-        <v>0.661558632264925</v>
+        <v>0.683911993066038</v>
       </c>
     </row>
     <row r="167">
@@ -4398,16 +4398,16 @@
         <v>28</v>
       </c>
       <c r="D167" t="n">
-        <v>0.0746840217475516</v>
+        <v>0.116717199295881</v>
       </c>
       <c r="E167" t="n">
-        <v>0.38152568808159</v>
+        <v>0.597868110487017</v>
       </c>
       <c r="F167" t="n">
-        <v>0.381881785089255</v>
+        <v>0.599238960995078</v>
       </c>
       <c r="G167" t="n">
-        <v>0.705652504032829</v>
+        <v>0.554199762067234</v>
       </c>
     </row>
     <row r="168">
@@ -4421,16 +4421,16 @@
         <v>28</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.0306522347664964</v>
+        <v>0.0228994540940675</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.156345320727427</v>
+        <v>0.116785179596976</v>
       </c>
       <c r="F168" t="n">
-        <v>0.156369819847143</v>
+        <v>0.116795390167078</v>
       </c>
       <c r="G168" t="n">
-        <v>0.876949379087478</v>
+        <v>0.907919714984244</v>
       </c>
     </row>
     <row r="169">
@@ -4441,19 +4441,19 @@
         <v>43</v>
       </c>
       <c r="C169" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D169" t="n">
-        <v>0.119024191579558</v>
+        <v>0.148782022711912</v>
       </c>
       <c r="E169" t="n">
-        <v>0.737208930259398</v>
+        <v>0.911773594330156</v>
       </c>
       <c r="F169" t="n">
-        <v>0.738967450917892</v>
+        <v>0.915191782284531</v>
       </c>
       <c r="G169" t="n">
-        <v>0.464467045884907</v>
+        <v>0.36601721881742</v>
       </c>
     </row>
     <row r="170">
@@ -4464,19 +4464,19 @@
         <v>44</v>
       </c>
       <c r="C170" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.103477804204626</v>
+        <v>-0.0453316547687223</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.631692031339127</v>
+        <v>-0.272176468041946</v>
       </c>
       <c r="F170" t="n">
-        <v>0.632828081231952</v>
+        <v>0.272269824132159</v>
       </c>
       <c r="G170" t="n">
-        <v>0.530737856879128</v>
+        <v>0.786970129016585</v>
       </c>
     </row>
     <row r="171">
@@ -4487,19 +4487,19 @@
         <v>45</v>
       </c>
       <c r="C171" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D171" t="n">
-        <v>0.00528310493277061</v>
+        <v>0.0304858109190382</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0279558237001832</v>
+        <v>0.158458021922533</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0279559537495381</v>
+        <v>0.158482583025731</v>
       </c>
       <c r="G171" t="n">
-        <v>0.977895587198966</v>
+        <v>0.875255982636691</v>
       </c>
     </row>
     <row r="172">
@@ -4510,19 +4510,19 @@
         <v>46</v>
       </c>
       <c r="C172" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.109938170712969</v>
+        <v>-0.130510405864228</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.634109696791174</v>
+        <v>-0.742513400339356</v>
       </c>
       <c r="F172" t="n">
-        <v>0.635398220982735</v>
+        <v>0.744647357875075</v>
       </c>
       <c r="G172" t="n">
-        <v>0.529550488919515</v>
+        <v>0.461918938101447</v>
       </c>
     </row>
     <row r="173">
@@ -4533,19 +4533,19 @@
         <v>47</v>
       </c>
       <c r="C173" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D173" t="n">
-        <v>0.388134400395836</v>
+        <v>0.402813128004068</v>
       </c>
       <c r="E173" t="n">
-        <v>2.20577243557233</v>
+        <v>2.25948430290454</v>
       </c>
       <c r="F173" t="n">
-        <v>2.26797027413912</v>
+        <v>2.32877534763431</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0309567287696687</v>
+        <v>0.0273138443983041</v>
       </c>
     </row>
     <row r="174">
@@ -4556,19 +4556,19 @@
         <v>48</v>
       </c>
       <c r="C174" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D174" t="n">
-        <v>0.275323431768839</v>
+        <v>0.274144081848399</v>
       </c>
       <c r="E174" t="n">
-        <v>1.52192742266829</v>
+        <v>1.48870708415362</v>
       </c>
       <c r="F174" t="n">
-        <v>1.54226816477022</v>
+        <v>1.50842391357974</v>
       </c>
       <c r="G174" t="n">
-        <v>0.133851243860785</v>
+        <v>0.142647987100722</v>
       </c>
     </row>
     <row r="175">
@@ -4582,16 +4582,16 @@
         <v>15</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.0720023878368345</v>
+        <v>-0.190305755284113</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.260058334911017</v>
+        <v>-0.694625298842939</v>
       </c>
       <c r="F175" t="n">
-        <v>0.260283878608836</v>
+        <v>0.698930199255053</v>
       </c>
       <c r="G175" t="n">
-        <v>0.798721916222673</v>
+        <v>0.496910402779085</v>
       </c>
     </row>
     <row r="176">
@@ -4605,16 +4605,16 @@
         <v>24</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.164076978119241</v>
+        <v>-0.126588688035128</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.776609090285788</v>
+        <v>-0.596955998439406</v>
       </c>
       <c r="F176" t="n">
-        <v>0.78016236478742</v>
+        <v>0.598568888475907</v>
       </c>
       <c r="G176" t="n">
-        <v>0.443608625063193</v>
+        <v>0.55557384662509</v>
       </c>
     </row>
     <row r="177">
@@ -4625,19 +4625,19 @@
         <v>51</v>
       </c>
       <c r="C177" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.0724498095710116</v>
+        <v>-0.0695084460100148</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.377121012571406</v>
+        <v>-0.35499737530722</v>
       </c>
       <c r="F177" t="n">
-        <v>0.377452175381409</v>
+        <v>0.355284226116525</v>
       </c>
       <c r="G177" t="n">
-        <v>0.708788412968723</v>
+        <v>0.725242785104046</v>
       </c>
     </row>
     <row r="178">
@@ -4648,19 +4648,19 @@
         <v>52</v>
       </c>
       <c r="C178" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.063997376657057</v>
+        <v>-0.0654977648492416</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.368140082242394</v>
+        <v>-0.371042503257347</v>
       </c>
       <c r="F178" t="n">
-        <v>0.368392118663547</v>
+        <v>0.371308614471966</v>
       </c>
       <c r="G178" t="n">
-        <v>0.714933652498206</v>
+        <v>0.71285483418086</v>
       </c>
     </row>
     <row r="179">
@@ -4671,19 +4671,19 @@
         <v>53</v>
       </c>
       <c r="C179" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D179" t="n">
-        <v>0.223425682824365</v>
+        <v>0.253513346109674</v>
       </c>
       <c r="E179" t="n">
-        <v>1.18087186739844</v>
+        <v>1.32148184971537</v>
       </c>
       <c r="F179" t="n">
-        <v>1.19106281895288</v>
+        <v>1.33632470257643</v>
       </c>
       <c r="G179" t="n">
-        <v>0.24399476739632</v>
+        <v>0.193021435807524</v>
       </c>
     </row>
     <row r="180">
@@ -4694,19 +4694,19 @@
         <v>54</v>
       </c>
       <c r="C180" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D180" t="n">
-        <v>0.0775416850361716</v>
+        <v>0.0993595880642934</v>
       </c>
       <c r="E180" t="n">
-        <v>0.403728884703501</v>
+        <v>0.508313651348712</v>
       </c>
       <c r="F180" t="n">
-        <v>0.404135220927819</v>
+        <v>0.509155989586128</v>
       </c>
       <c r="G180" t="n">
-        <v>0.689296697037374</v>
+        <v>0.614937059654582</v>
       </c>
     </row>
     <row r="181">
@@ -4720,16 +4720,16 @@
         <v>15</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.152659151432828</v>
+        <v>-0.281286633715969</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.554757015522662</v>
+        <v>-1.04228809799712</v>
       </c>
       <c r="F181" t="n">
-        <v>0.556948446797277</v>
+        <v>1.05686560220718</v>
       </c>
       <c r="G181" t="n">
-        <v>0.587023678384602</v>
+        <v>0.309817805751433</v>
       </c>
     </row>
     <row r="182">
@@ -4743,16 +4743,16 @@
         <v>23</v>
       </c>
       <c r="D182" t="n">
-        <v>0.0315786169512351</v>
+        <v>0.0787555945368906</v>
       </c>
       <c r="E182" t="n">
-        <v>0.144759533829194</v>
+        <v>0.361652423696609</v>
       </c>
       <c r="F182" t="n">
-        <v>0.144783610290232</v>
+        <v>0.36202794868184</v>
       </c>
       <c r="G182" t="n">
-        <v>0.886262288634575</v>
+        <v>0.720948674466253</v>
       </c>
     </row>
     <row r="183">
@@ -4763,19 +4763,19 @@
         <v>57</v>
       </c>
       <c r="C183" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.208615743577926</v>
+        <v>-0.20553548999355</v>
       </c>
       <c r="E183" t="n">
-        <v>-1.30515233979693</v>
+        <v>-1.26828890098537</v>
       </c>
       <c r="F183" t="n">
-        <v>1.31492520984448</v>
+        <v>1.27749860322557</v>
       </c>
       <c r="G183" t="n">
-        <v>0.196415461945504</v>
+        <v>0.209384242064382</v>
       </c>
     </row>
     <row r="184">
@@ -4786,19 +4786,19 @@
         <v>58</v>
       </c>
       <c r="C184" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D184" t="n">
-        <v>0.0614060653499153</v>
+        <v>0.0496684388898769</v>
       </c>
       <c r="E184" t="n">
-        <v>0.37398905449087</v>
+        <v>0.298256056200209</v>
       </c>
       <c r="F184" t="n">
-        <v>0.374224725296912</v>
+        <v>0.298378904095144</v>
       </c>
       <c r="G184" t="n">
-        <v>0.7103732834075</v>
+        <v>0.767129471972964</v>
       </c>
     </row>
     <row r="185">
@@ -4809,19 +4809,19 @@
         <v>59</v>
       </c>
       <c r="C185" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D185" t="n">
-        <v>0.33461374633246</v>
+        <v>0.319043939848369</v>
       </c>
       <c r="E185" t="n">
-        <v>2.08808848728053</v>
+        <v>1.95575150907219</v>
       </c>
       <c r="F185" t="n">
-        <v>2.13049402046346</v>
+        <v>1.99156894598558</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0400332285754671</v>
+        <v>0.054267411798257</v>
       </c>
     </row>
     <row r="186">
@@ -4832,19 +4832,19 @@
         <v>60</v>
       </c>
       <c r="C186" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D186" t="n">
-        <v>0.263759757256762</v>
+        <v>0.289825819911713</v>
       </c>
       <c r="E186" t="n">
-        <v>1.59819939946048</v>
+        <v>1.73981668829155</v>
       </c>
       <c r="F186" t="n">
-        <v>1.617709439512</v>
+        <v>1.7657473338553</v>
       </c>
       <c r="G186" t="n">
-        <v>0.114703619400397</v>
+        <v>0.0864179530739032</v>
       </c>
     </row>
     <row r="187">
@@ -4855,19 +4855,19 @@
         <v>61</v>
       </c>
       <c r="C187" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D187" t="n">
-        <v>0.0776751077936847</v>
+        <v>0.0485745926012179</v>
       </c>
       <c r="E187" t="n">
-        <v>0.533588563845483</v>
+        <v>0.329708393847199</v>
       </c>
       <c r="F187" t="n">
-        <v>0.534127456139276</v>
+        <v>0.329838270846304</v>
       </c>
       <c r="G187" t="n">
-        <v>0.595770894648492</v>
+        <v>0.74301955205962</v>
       </c>
     </row>
     <row r="188">
@@ -4878,19 +4878,19 @@
         <v>62</v>
       </c>
       <c r="C188" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D188" t="n">
-        <v>0.127055163230331</v>
+        <v>0.114870911038741</v>
       </c>
       <c r="E188" t="n">
-        <v>0.787476439009581</v>
+        <v>0.701830371698227</v>
       </c>
       <c r="F188" t="n">
-        <v>0.789619982075094</v>
+        <v>0.703388605336171</v>
       </c>
       <c r="G188" t="n">
-        <v>0.434649388341528</v>
+        <v>0.486216516434878</v>
       </c>
     </row>
     <row r="189">
@@ -4901,19 +4901,19 @@
         <v>63</v>
       </c>
       <c r="C189" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D189" t="n">
-        <v>0.156119154323163</v>
+        <v>0.177285230039652</v>
       </c>
       <c r="E189" t="n">
-        <v>0.970318253528832</v>
+        <v>1.08989980172856</v>
       </c>
       <c r="F189" t="n">
-        <v>0.974330113462626</v>
+        <v>1.09574102583462</v>
       </c>
       <c r="G189" t="n">
-        <v>0.33605454896471</v>
+        <v>0.28027337043901</v>
       </c>
     </row>
     <row r="190">
@@ -4927,16 +4927,16 @@
         <v>40</v>
       </c>
       <c r="D190" t="n">
-        <v>0.119862787250873</v>
+        <v>0.112970803068548</v>
       </c>
       <c r="E190" t="n">
-        <v>0.742453200156289</v>
+        <v>0.699384268870576</v>
       </c>
       <c r="F190" t="n">
-        <v>0.744249535425318</v>
+        <v>0.700885654451687</v>
       </c>
       <c r="G190" t="n">
-        <v>0.461303335637904</v>
+        <v>0.487644270767467</v>
       </c>
     </row>
     <row r="191">
@@ -4950,16 +4950,16 @@
         <v>40</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.0852262471708933</v>
+        <v>-0.0897119790991358</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.526647454297064</v>
+        <v>-0.55451260313044</v>
       </c>
       <c r="F191" t="n">
-        <v>0.527288344470238</v>
+        <v>0.555260729778125</v>
       </c>
       <c r="G191" t="n">
-        <v>0.601058564921348</v>
+        <v>0.581970599991815</v>
       </c>
     </row>
     <row r="192">
@@ -4970,19 +4970,19 @@
         <v>66</v>
       </c>
       <c r="C192" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.207112994250088</v>
+        <v>-0.174375178231932</v>
       </c>
       <c r="E192" t="n">
-        <v>-1.42532736805131</v>
+        <v>-1.18182139165476</v>
       </c>
       <c r="F192" t="n">
-        <v>1.43584199226386</v>
+        <v>1.18794441236904</v>
       </c>
       <c r="G192" t="n">
-        <v>0.157813113081912</v>
+        <v>0.241087621424739</v>
       </c>
     </row>
     <row r="193">
@@ -4993,19 +4993,19 @@
         <v>67</v>
       </c>
       <c r="C193" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D193" t="n">
-        <v>0.128649770876028</v>
+        <v>0.0975226779652002</v>
       </c>
       <c r="E193" t="n">
-        <v>0.886893097192272</v>
+        <v>0.663539914894613</v>
       </c>
       <c r="F193" t="n">
-        <v>0.88936896880508</v>
+        <v>0.664598924537172</v>
       </c>
       <c r="G193" t="n">
-        <v>0.378334427569818</v>
+        <v>0.509625193727625</v>
       </c>
     </row>
     <row r="194">
@@ -5016,19 +5016,19 @@
         <v>68</v>
       </c>
       <c r="C194" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D194" t="n">
-        <v>0.0153773952615313</v>
+        <v>0.017490912063863</v>
       </c>
       <c r="E194" t="n">
-        <v>0.105430421267379</v>
+        <v>0.118641237027306</v>
       </c>
       <c r="F194" t="n">
-        <v>0.105434577059857</v>
+        <v>0.118647287712546</v>
       </c>
       <c r="G194" t="n">
-        <v>0.916479681192154</v>
+        <v>0.906071417590539</v>
       </c>
     </row>
     <row r="195">
@@ -5039,19 +5039,19 @@
         <v>69</v>
       </c>
       <c r="C195" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D195" t="n">
-        <v>0.171036731852872</v>
+        <v>0.12711224798789</v>
       </c>
       <c r="E195" t="n">
-        <v>1.18420767714253</v>
+        <v>0.866805977088933</v>
       </c>
       <c r="F195" t="n">
-        <v>1.19010537326314</v>
+        <v>0.869167603983637</v>
       </c>
       <c r="G195" t="n">
-        <v>0.239981837911637</v>
+        <v>0.389268071591976</v>
       </c>
     </row>
     <row r="196">
@@ -5062,19 +5062,19 @@
         <v>70</v>
       </c>
       <c r="C196" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D196" t="n">
-        <v>0.045016765613576</v>
+        <v>0.0301675742486452</v>
       </c>
       <c r="E196" t="n">
-        <v>0.308828123472486</v>
+        <v>0.204668546843476</v>
       </c>
       <c r="F196" t="n">
-        <v>0.308932582381058</v>
+        <v>0.204699611317904</v>
       </c>
       <c r="G196" t="n">
-        <v>0.758738136371332</v>
+        <v>0.838709887534541</v>
       </c>
     </row>
     <row r="197">
@@ -5085,19 +5085,19 @@
         <v>71</v>
       </c>
       <c r="C197" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D197" t="n">
-        <v>0.120216738088581</v>
+        <v>0.093798674846893</v>
       </c>
       <c r="E197" t="n">
-        <v>0.828169512719265</v>
+        <v>0.638049201716177</v>
       </c>
       <c r="F197" t="n">
-        <v>0.83018521080226</v>
+        <v>0.63899075651972</v>
       </c>
       <c r="G197" t="n">
-        <v>0.410631263272887</v>
+        <v>0.525998141562142</v>
       </c>
     </row>
     <row r="198">
@@ -5108,19 +5108,19 @@
         <v>72</v>
       </c>
       <c r="C198" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D198" t="n">
-        <v>0.0970718632524359</v>
+        <v>0.0744849736970384</v>
       </c>
       <c r="E198" t="n">
-        <v>0.667593359969234</v>
+        <v>0.506119043923605</v>
       </c>
       <c r="F198" t="n">
-        <v>0.668648944035662</v>
+        <v>0.506588905439042</v>
       </c>
       <c r="G198" t="n">
-        <v>0.506990396237877</v>
+        <v>0.614862995165425</v>
       </c>
     </row>
     <row r="199">
@@ -5131,19 +5131,19 @@
         <v>73</v>
       </c>
       <c r="C199" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D199" t="n">
-        <v>0.0807914344488112</v>
+        <v>0.0464834940589691</v>
       </c>
       <c r="E199" t="n">
-        <v>0.555088012484597</v>
+        <v>0.315493757274244</v>
       </c>
       <c r="F199" t="n">
-        <v>0.555694719188282</v>
+        <v>0.315607548877253</v>
       </c>
       <c r="G199" t="n">
-        <v>0.58105531086332</v>
+        <v>0.753727891535153</v>
       </c>
     </row>
   </sheetData>
@@ -5188,19 +5188,19 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.515073899744472</v>
+        <v>-0.496089317063126</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.79051502076809</v>
+        <v>-2.60943788855276</v>
       </c>
       <c r="F2" t="n">
-        <v>2.94388252860142</v>
+        <v>2.74011158734887</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00708808310766655</v>
+        <v>0.0116644409538978</v>
       </c>
     </row>
     <row r="3">
@@ -5211,19 +5211,19 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.296045814906635</v>
+        <v>-0.302641652371087</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.09220850383557</v>
+        <v>-2.11896983394365</v>
       </c>
       <c r="F3" t="n">
-        <v>2.12483631594728</v>
+        <v>2.15361036607498</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03888772500955</v>
+        <v>0.0365458322840949</v>
       </c>
     </row>
     <row r="4">
@@ -5234,19 +5234,19 @@
         <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.333960216342577</v>
+        <v>-0.325930711359295</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.11241568639184</v>
+        <v>-2.0296110232128</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1551329725877</v>
+        <v>2.06853964857648</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0377278688166482</v>
+        <v>0.0458296420509902</v>
       </c>
     </row>
     <row r="5">
@@ -5257,19 +5257,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.291831197021003</v>
+        <v>-0.284759382666505</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.06058194502606</v>
+        <v>-1.98623149884413</v>
       </c>
       <c r="F5" t="n">
-        <v>2.09174801685831</v>
+        <v>2.01474448152851</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0418903392530171</v>
+        <v>0.0497985408504496</v>
       </c>
     </row>
     <row r="6">
@@ -5280,19 +5280,19 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>0.559293550374664</v>
+        <v>0.535795567871452</v>
       </c>
       <c r="E6" t="n">
-        <v>3.09519762401933</v>
+        <v>2.86905529947725</v>
       </c>
       <c r="F6" t="n">
-        <v>3.30526882642754</v>
+        <v>3.04327843444062</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00297341444136559</v>
+        <v>0.00577173078303921</v>
       </c>
     </row>
     <row r="7">
@@ -5303,19 +5303,19 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>0.309901976794455</v>
+        <v>0.322088522772133</v>
       </c>
       <c r="E7" t="n">
-        <v>2.19680517518906</v>
+        <v>2.26513294445982</v>
       </c>
       <c r="F7" t="n">
-        <v>2.23459326267259</v>
+        <v>2.3074771256713</v>
       </c>
       <c r="G7" t="n">
-        <v>0.030236958345378</v>
+        <v>0.0255794074942179</v>
       </c>
     </row>
     <row r="8">
@@ -5326,19 +5326,19 @@
         <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>0.345304111173864</v>
+        <v>0.359243701398886</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1904165813151</v>
+        <v>2.25610358068492</v>
       </c>
       <c r="F8" t="n">
-        <v>2.23806435048675</v>
+        <v>2.3096453917963</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0313205833231369</v>
+        <v>0.0267544481444679</v>
       </c>
     </row>
     <row r="9">
@@ -5349,19 +5349,19 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.316030270025639</v>
+        <v>-0.318820381942931</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.06958882574934</v>
+        <v>-2.06293185363757</v>
       </c>
       <c r="F9" t="n">
-        <v>2.10672232573751</v>
+        <v>2.10065500746679</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0414614499045388</v>
+        <v>0.0421866108506569</v>
       </c>
     </row>
     <row r="10">
@@ -5372,42 +5372,19 @@
         <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>0.388134400395836</v>
+        <v>0.402813128004068</v>
       </c>
       <c r="E10" t="n">
-        <v>2.20577243557233</v>
+        <v>2.25948430290454</v>
       </c>
       <c r="F10" t="n">
-        <v>2.26797027413912</v>
+        <v>2.32877534763431</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0309567287696687</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" t="n">
-        <v>38</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.33461374633246</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.08808848728053</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.13049402046346</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0400332285754671</v>
+        <v>0.0273138443983041</v>
       </c>
     </row>
   </sheetData>
